--- a/naver-place-crawler/results_nail/북구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/북구_네일샵.xlsx
@@ -564,39 +564,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일수미</t>
+          <t>Nail Vivienne</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rawith0411@naver.com</t>
+          <t>spotv_sports@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1362-2568</t>
+          <t>0507-1352-1254</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로 8 1F 18호</t>
+          <t>대구광역시 북구 한강로 72-1 비비엔느네일</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_SIxixlxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -612,22 +612,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1461190392</t>
+          <t>1234676332</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1461190392</t>
+          <t>https://m.place.naver.com/place/1234676332</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>모제스튜디오</t>
+          <t>살롱드302</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>possam-@naver.com</t>
+          <t>hanseon216@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1360-2673</t>
+          <t>0507-1366-7799</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로31길 1 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로 434 2층 206호 살롱드302</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moje_nailstudio?igsh=emdzbm4xMmJhd2dl</t>
+          <t>https://linkfly.to/70627DEJDap</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,22 +706,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>887</v>
+        <v>394</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R3" t="n">
-        <v>892</v>
+        <v>405</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1258515201</t>
+          <t>1472140745</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258515201</t>
+          <t>https://m.place.naver.com/place/1472140745</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -752,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일105 복현 본점</t>
+          <t>하까네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nail105@naver.com</t>
+          <t>bluefrog385@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1324-0222</t>
+          <t>0507-1394-0637</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 223 1층</t>
+          <t>대구광역시 북구 학남로 9 1층 하까네일&amp;래쉬</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail.105</t>
+          <t>https://www.instagram.com/hakkanail</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1339</v>
+        <v>134</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>1380</v>
+        <v>138</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1205043851</t>
+          <t>1721951293</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205043851</t>
+          <t>https://m.place.naver.com/place/1721951293</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>THE예쁘다</t>
+          <t>모리앤네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>theprettyjjy@naver.com</t>
+          <t>cute880201@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1311-7059</t>
+          <t>0507-1362-4607</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태암로 8 1층</t>
+          <t>대구광역시 북구 성북로 70 침산화성파크드림1008동 상가2층 222호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://linktr.ee/theprettynail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -894,22 +894,22 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>260</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>281</v>
+        <v>9</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1626649044</t>
+          <t>1109464508</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1626649044</t>
+          <t>https://m.place.naver.com/place/1109464508</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>네일 르 마지</t>
+          <t>화야네일앤뷰티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hihy925@naver.com</t>
+          <t>sbsb100488@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1360-8063</t>
+          <t>0507-1319-6498</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀오피스텔 상가 2층 201호</t>
+          <t>대구광역시 북구 팔달로35길 4 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lemazi</t>
+          <t>http://www.instagram.com/hwaya_beauty</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="R6" t="n">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1295693572</t>
+          <t>1283528001</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1295693572</t>
+          <t>https://m.place.naver.com/place/1283528001</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>온도네일</t>
+          <t>애몽</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>yunparadise@naver.com</t>
+          <t>emong0902@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1388-6141</t>
+          <t>0507-1332-4233</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로26길 15-7 1층 온도네일</t>
+          <t>대구광역시 북구 매전로 50-14 1층, 애몽</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_anxlAs</t>
+          <t>https://www.instagram.com/nail_aemong</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>27</v>
+        <v>551</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="R7" t="n">
-        <v>40</v>
+        <v>585</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1397849384</t>
+          <t>1174913259</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1397849384</t>
+          <t>https://m.place.naver.com/place/1174913259</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1128,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>시월의 네일</t>
+          <t>밸리네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chltys1@naver.com</t>
+          <t>cosvalleycosmetics@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1368-1165</t>
+          <t>0507-1326-5359</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로105길 22 시월의 네일</t>
+          <t>대구광역시 북구 연경중앙로 11 금성백조예미지상가 1층 밸리네일</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_DwWvb</t>
+          <t>https://www.instagram.com/nail.vally</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1176,7 +1176,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1443846421</t>
+          <t>1585312708</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1443846421</t>
+          <t>https://m.place.naver.com/place/1585312708</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,34 +1222,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>손빛네일</t>
+          <t>가비뷰티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>son_b_nail@naver.com</t>
+          <t>dadalover0407@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1418-5899</t>
+          <t>0507-1315-8548</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 신암로 57 1층</t>
+          <t>대구광역시 북구 태전로3길 17-1 1층 (태전동)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/son_b_nail</t>
+          <t>http://pf.kakao.com/_evbSxj</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>125</v>
+        <v>67</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1948109577</t>
+          <t>1054977148</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948109577</t>
+          <t>https://m.place.naver.com/place/1054977148</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>리리네일</t>
+          <t>네일바다</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hime_s2@naver.com</t>
+          <t>kiwi10041010@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1379-6902</t>
+          <t>0507-1317-2364</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정동로 76 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로108길 21 1층 네일바다</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hime_s2</t>
+          <t>http://instagram.com/nail.bada</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>289</v>
+        <v>2</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1536988597</t>
+          <t>1756678430</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1536988597</t>
+          <t>https://m.place.naver.com/place/1756678430</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일다니</t>
+          <t>온유뷰티</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nail_dani@naver.com</t>
+          <t>nhbnhb05@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1326-6288</t>
+          <t>0507-1433-0601</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태암남로11길 28-1 네일다니</t>
+          <t>대구광역시 북구 칠성남로 30 상가동 102호 온유뷰티</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_dani</t>
+          <t>https://instagram.com/on._u_beauty?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1458,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>412</v>
+        <v>69</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>436</v>
+        <v>79</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1058398706</t>
+          <t>1391715445</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058398706</t>
+          <t>https://m.place.naver.com/place/1391715445</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1504,39 +1504,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>은뷰티</t>
+          <t>루미포레네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bazilamy@naver.com</t>
+          <t>uilll77@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1366-9360</t>
+          <t>0507-1377-3829</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로22길 5 102동 112호 은뷰티</t>
+          <t>대구광역시 북구 동북로 163 202동 107호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_xhpAyn</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1552,22 +1552,22 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="Q12" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2094752142</t>
+          <t>2023409739</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094752142</t>
+          <t>https://m.place.naver.com/place/2023409739</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1598,29 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엔케어센터 복현점 /내성발톱/발각질/무좀발톱/젤네일</t>
+          <t>네일 르 마지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ncarecenter@naver.com</t>
+          <t>hihy925@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1326-8241</t>
+          <t>0507-1360-8063</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 12층 1206호</t>
+          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀오피스텔 상가 2층 201호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://abalico.co.kr</t>
+          <t>https://www.instagram.com/nail_lemazi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1646,7 +1646,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>703</v>
+        <v>185</v>
       </c>
       <c r="Q13" t="n">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>771</v>
+        <v>193</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,17 +1670,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1956967552</t>
+          <t>1295693572</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956967552</t>
+          <t>https://m.place.naver.com/place/1295693572</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>설레는 네일</t>
+          <t>비쥬네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>woori8999@naver.com</t>
+          <t>h2425@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1460-0172</t>
+          <t>053-264-1130</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 131 양우내안에아파트 상가 1층</t>
+          <t>대구광역시 북구 동천로23길 2 동천골든프라자 1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sullem_mn</t>
+          <t>https://www.instagram.com/bijounail/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1749,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>246</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="R14" t="n">
-        <v>267</v>
+        <v>71</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,17 +1764,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1264344506</t>
+          <t>36827317</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264344506</t>
+          <t>https://m.place.naver.com/place/36827317</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1786,29 +1786,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>비니뷰티샵</t>
+          <t>원뷰티</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mssjse@naver.com</t>
+          <t>wmk3669@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1423-7769</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로109길 12 1층</t>
+          <t>대구광역시 북구 칠성로 4 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s3QEI0nh</t>
+          <t>https://smartstore.naver.com/one_beauty</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1834,7 +1830,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1843,13 +1839,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R15" t="n">
-        <v>50</v>
+        <v>124</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1858,17 +1854,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1794625110</t>
+          <t>1885875370</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794625110</t>
+          <t>https://m.place.naver.com/place/1885875370</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1880,34 +1876,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>살롱드302</t>
+          <t>오아이뷰티</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hanseon216@naver.com</t>
+          <t>mycutegod@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1366-7799</t>
+          <t>0507-1339-2823</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 434 2층 206호 살롱드302</t>
+          <t>대구광역시 북구 칠성남로 70 근린생활시설 207호(2층)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://linkfly.to/70627DEJDap</t>
+          <t>http://www.instagram.com/oi_b.room</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1933,17 +1929,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>392</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="R16" t="n">
-        <v>403</v>
+        <v>31</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,17 +1948,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1472140745</t>
+          <t>1302335033</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472140745</t>
+          <t>https://m.place.naver.com/place/1302335033</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1974,25 +1970,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>원뷰티</t>
+          <t>네일피오나</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wmk3669@naver.com</t>
+          <t>cjrut2674@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1364-8481</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성로 4 2층</t>
+          <t>대구광역시 북구 매전로4길 22 1층 네일 피오나</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/one_beauty</t>
+          <t>https://www.instagram.com/nail_piona</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1885875370</t>
+          <t>1410565139</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1885875370</t>
+          <t>https://m.place.naver.com/place/1410565139</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2064,29 +2064,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>네일도 왁싱</t>
+          <t>에이네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cuiyushan20-19@naver.com</t>
+          <t>hajw0129@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1395-1355</t>
+          <t>0507-1489-5668</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로 70 상가동 2층 210호</t>
+          <t>대구광역시 북구 학정로 426 하나은행건물 3층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://카카오톡오픈채팅을시작해보세요.링크를선택하면카카오톡이실행됩니다.네일도왁싱https//open.kakao.com/o/suNdDW4g</t>
+          <t>https://www.instagram.com/a.nail0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2112,7 +2112,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>260</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="R18" t="n">
-        <v>379</v>
+        <v>40</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,17 +2136,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1132125501</t>
+          <t>1014010899</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132125501</t>
+          <t>https://m.place.naver.com/place/1014010899</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2252,39 +2252,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>세니요미</t>
+          <t>은뷰티</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sennny@naver.com</t>
+          <t>akswb110@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1471-0523</t>
+          <t>0507-1366-9360</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로7길 6-16 1층 세니요미</t>
+          <t>대구광역시 북구 침산로22길 5 102동 112호 은뷰티</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://instabio.cc/4021506dbM8cU</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2300,22 +2300,22 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>265</v>
+        <v>45</v>
       </c>
       <c r="Q20" t="n">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="R20" t="n">
-        <v>350</v>
+        <v>76</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2324,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1033303518</t>
+          <t>2094752142</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033303518</t>
+          <t>https://m.place.naver.com/place/2094752142</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2346,29 +2346,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>채희뷰티</t>
+          <t>몽뎅네일스튜디오</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>chaehee_beauty@naver.com</t>
+          <t>pk2hee@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1414-6681</t>
+          <t>0507-1314-6829</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 247 상가동 2층 210호</t>
+          <t>대구광역시 북구 학정동로 40 한라하우젠트2차 상가</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaehee_beauty</t>
+          <t>https://www.instagram.com/mongdeng_nail</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2394,7 +2394,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>514</v>
+        <v>170</v>
       </c>
       <c r="Q21" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="R21" t="n">
-        <v>565</v>
+        <v>181</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1030745191</t>
+          <t>1973307356</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030745191</t>
+          <t>https://m.place.naver.com/place/1973307356</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2440,34 +2440,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>레푸스 칠곡점</t>
+          <t>유어메리뷰티</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>hjw8125@naver.com</t>
+          <t>multtang1@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1319-8125</t>
+          <t>0507-1378-9783</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 244 3층</t>
+          <t>대구광역시 북구 복현로20길 2 1층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hjw8125</t>
+          <t>http://pf.kakao.com/_mBAAn</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2488,22 +2488,22 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="Q22" t="n">
-        <v>356</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>507</v>
+        <v>159</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,17 +2512,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1036282232</t>
+          <t>1050332478</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036282232</t>
+          <t>https://m.place.naver.com/place/1050332478</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2534,30 +2534,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일플루이</t>
+          <t>꼬미네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nailpluie@naver.com</t>
+          <t>xoxo6514@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1398-9513</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로110길 19 1층</t>
+          <t>대구광역시 북구 한강로6길 7-4 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailpluie</t>
+          <t>https://www.instagram.com/p/CUdrackv2Uh/?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2587,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2606,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1974701574</t>
+          <t>1695465470</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1974701574</t>
+          <t>https://m.place.naver.com/place/1695465470</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2624,29 +2628,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>어제오늘네일</t>
+          <t>네일라쥬르</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ksunmi88@naver.com</t>
+          <t>dkenl0103@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1384-2440</t>
+          <t>0507-1371-0767</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동암로 110 3층 어제오늘네일</t>
+          <t>대구광역시 북구 팔달로 223</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeto.nail2</t>
+          <t>https://www.instagram.com/lasure_nail</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2681,13 +2685,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>711</v>
+        <v>38</v>
       </c>
       <c r="Q24" t="n">
-        <v>172</v>
+        <v>44</v>
       </c>
       <c r="R24" t="n">
-        <v>883</v>
+        <v>82</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2700,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1950980170</t>
+          <t>1303390693</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1950980170</t>
+          <t>https://m.place.naver.com/place/1303390693</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2718,29 +2722,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>화야네일앤뷰티</t>
+          <t>민이네일</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>sbsb100488@naver.com</t>
+          <t>lee_dormery@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1319-6498</t>
+          <t>0507-1405-3361</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로35길 4 1층</t>
+          <t>대구광역시 북구 대동로 50 1층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hwaya_beauty</t>
+          <t>https://www.instagram.com/_mi.ni_nail</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2766,7 +2770,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2775,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>311</v>
+        <v>1</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2794,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1283528001</t>
+          <t>1867922573</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283528001</t>
+          <t>https://m.place.naver.com/place/1867922573</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2812,34 +2816,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>모카네일</t>
+          <t>레푸스 칠곡점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>daonnail0305@naver.com</t>
+          <t>hjw8125@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1446-1569</t>
+          <t>0507-1319-8125</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정동로13길 3 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로 244 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcubwn</t>
+          <t>https://blog.naver.com/hjw8125</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2849,7 +2853,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2860,22 +2864,22 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>479</v>
+        <v>151</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>356</v>
       </c>
       <c r="R26" t="n">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,17 +2888,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1744601857</t>
+          <t>1036282232</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1744601857</t>
+          <t>https://m.place.naver.com/place/1036282232</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2906,25 +2910,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>공원옆네일</t>
+          <t>뮤니크네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>hymizzang@naver.com</t>
+          <t>tngus4051@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1375-6408</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로21길 37 302동 208호</t>
+          <t>대구광역시 북구 팔거천동로34길 16-19 1층 뮤니크네일</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.park_</t>
+          <t>https://www.instagram.com/munick_nail</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2959,13 +2967,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R27" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2982,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1948302097</t>
+          <t>1805790304</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948302097</t>
+          <t>https://m.place.naver.com/place/1805790304</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2996,34 +3004,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>유어메리뷰티</t>
+          <t>손빛네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>multtang1@naver.com</t>
+          <t>son_b_nail@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1378-9783</t>
+          <t>0507-1418-5899</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로20길 2 1층</t>
+          <t>대구광역시 북구 신암로 57 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_mBAAn</t>
+          <t>https://blog.naver.com/son_b_nail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3033,7 +3041,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3044,7 +3052,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3053,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R28" t="n">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3068,17 +3076,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1050332478</t>
+          <t>1948109577</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050332478</t>
+          <t>https://m.place.naver.com/place/1948109577</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3090,34 +3098,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>플로우네일케어</t>
+          <t>네일,해주연</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>frhlkfhkly3@naver.com</t>
+          <t>vely_sohee@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0507-1356-1202</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경지묘로 6 1층 108호</t>
+          <t>대구광역시 북구 매전로4길 31 매천동753</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flow_nail_care/</t>
+          <t>http://pf.kakao.com/_nzuin</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3138,22 +3142,22 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3162,17 +3166,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1644153139</t>
+          <t>2041500566</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644153139</t>
+          <t>https://m.place.naver.com/place/2041500566</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3184,39 +3188,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>투모로우바이뷰티</t>
+          <t>멜리플루</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>yunsm04@naver.com</t>
+          <t>sycep@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1462-8557</t>
+          <t>0507-1388-1137</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로67길 20 1층</t>
+          <t>대구광역시 북구 대동로 38 1층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tomorrow_by_beauty</t>
+          <t>https://toss.place/_lb/TYwXvAttF</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3232,7 +3236,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3241,13 +3245,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>579</v>
+        <v>101</v>
       </c>
       <c r="Q30" t="n">
-        <v>215</v>
+        <v>23</v>
       </c>
       <c r="R30" t="n">
-        <v>794</v>
+        <v>124</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3256,17 +3260,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1006662497</t>
+          <t>1330782670</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006662497</t>
+          <t>https://m.place.naver.com/place/1330782670</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3278,29 +3282,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>이든네일</t>
+          <t>레몬 네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ansdkfma0822@naver.com</t>
+          <t>gorgeous_na_@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1381-2723</t>
+          <t>0507-1430-2811</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 북구 고성북로 34 오페라트루엘시민의숲 상가 201호</t>
+          <t>대구광역시 북구 호국로43길 27 . 상가 1층 북측</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/edeun_nail</t>
+          <t>https://www.instagram.com/lemon___nail</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3335,13 +3339,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="Q31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>161</v>
+        <v>18</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3350,17 +3354,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1221641229</t>
+          <t>1070857201</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221641229</t>
+          <t>https://m.place.naver.com/place/1070857201</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3372,29 +3376,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>뷰랩</t>
+          <t>이든네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>miheynog@naver.com</t>
+          <t>ansdkfma0822@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1417-9885</t>
+          <t>0507-1381-2723</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 97 영남네오빌아트 106동 앞 상가</t>
+          <t>대구광역시 북구 고성북로 34 오페라트루엘시민의숲 상가 201호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/viewlab</t>
+          <t>https://www.instagram.com/edeun_nail</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3429,13 +3433,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1387</v>
+        <v>160</v>
       </c>
       <c r="Q32" t="n">
-        <v>675</v>
+        <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>2062</v>
+        <v>162</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3444,17 +3448,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1602365195</t>
+          <t>1221641229</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602365195</t>
+          <t>https://m.place.naver.com/place/1221641229</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3466,29 +3470,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>밸리네일</t>
+          <t>엔뉴아네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>cosvalleycosmetics@naver.com</t>
+          <t>gkstnqls0858@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1326-5359</t>
+          <t>0507-1480-4144</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경중앙로 11 금성백조예미지상가 1층 밸리네일</t>
+          <t>대구광역시 북구 구암로22길 14 칠곡에덴타운 상가1층 엔뉴아네일</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.vally</t>
+          <t>https://www.instagram.com/nail_n.newa?igsh=MW94emM2YnNsNndkNQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3523,13 +3527,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3538,17 +3542,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1585312708</t>
+          <t>1900044418</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1585312708</t>
+          <t>https://m.place.naver.com/place/1900044418</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3560,34 +3564,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>애몽</t>
+          <t>비니뷰티샵</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>haranalice@naver.com</t>
+          <t>wooscarlet1007@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1332-4233</t>
+          <t>0507-1423-7769</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매전로 50-14 1층, 애몽</t>
+          <t>대구광역시 북구 학정로109길 12 1층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_aemong</t>
+          <t>https://open.kakao.com/o/s3QEI0nh</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3608,7 +3612,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3617,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>545</v>
+        <v>14</v>
       </c>
       <c r="Q34" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R34" t="n">
-        <v>579</v>
+        <v>50</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,17 +3636,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1174913259</t>
+          <t>1794625110</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174913259</t>
+          <t>https://m.place.naver.com/place/1794625110</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3654,29 +3658,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>오아이뷰티</t>
+          <t>아띠네일</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>mycutegod@naver.com</t>
+          <t>attinail_@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0507-1339-2823</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 70 근린생활시설 207호(2층)</t>
+          <t>대구광역시 북구 호국로57길 31-12 1층 아띠네일</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/oi_b.room</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3707,17 +3707,17 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q35" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3726,17 +3726,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1302335033</t>
+          <t>1088451483</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302335033</t>
+          <t>https://m.place.naver.com/place/1088451483</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3748,24 +3748,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nail Vivienne</t>
+          <t>그래비네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>spotv_sports@naver.com</t>
+          <t>foryou48613@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0507-1352-1254</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대구광역시 북구 한강로 72-1 비비엔느네일</t>
+          <t>대구광역시 북구 대천로18길 21 1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3805,13 +3801,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,17 +3816,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1234676332</t>
+          <t>1564740881</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234676332</t>
+          <t>https://m.place.naver.com/place/1564740881</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3842,25 +3838,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>미닛트 네일</t>
+          <t>갓네일 &amp; 뷰티 대구역점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dmsghk057@naver.com</t>
+          <t>god_nail_2000@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1432-2418</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로126길 7-12 105호</t>
+          <t>대구광역시 북구 중앙대로 513 2층 202호 갓네일 대구역점</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/minute_nail_/</t>
+          <t>https://www.instagram.com/god_nail_8000</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>47</v>
+        <v>441</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="R37" t="n">
-        <v>54</v>
+        <v>533</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3910,17 +3910,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1139512492</t>
+          <t>1364996819</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139512492</t>
+          <t>https://m.place.naver.com/place/1364996819</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3932,29 +3932,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>알미네일</t>
+          <t>모제스튜디오</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>choitattoo@naver.com</t>
+          <t>possam-@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1487-3656</t>
+          <t>0507-1360-2673</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로53길 24 1층</t>
+          <t>대구광역시 북구 침산남로31길 1 1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>http://instagram.com/ar_my_nail</t>
+          <t>https://www.instagram.com/moje_nailstudio?igsh=emdzbm4xMmJhd2dl</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3974,14 +3974,10 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>O</t>
@@ -3993,13 +3989,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>165</v>
+        <v>907</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>178</v>
+        <v>912</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +4004,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1406194751</t>
+          <t>1258515201</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406194751</t>
+          <t>https://m.place.naver.com/place/1258515201</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4030,29 +4026,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>꼬미네일</t>
+          <t>시월의 네일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>woosj7243@naver.com</t>
+          <t>chltys1@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1398-9513</t>
+          <t>0507-1368-1165</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 북구 한강로6길 7-4 1층</t>
+          <t>대구광역시 북구 중앙대로105길 22 시월의 네일</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CUdrackv2Uh/?utm_medium=copy_link</t>
+          <t>http://pf.kakao.com/_DwWvb</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4067,7 +4063,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4078,7 +4074,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4087,13 +4083,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="R39" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,17 +4098,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1695465470</t>
+          <t>1443846421</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695465470</t>
+          <t>https://m.place.naver.com/place/1443846421</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4124,34 +4120,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>마이영네일</t>
+          <t>네일블링츠</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>yujinlee10@naver.com</t>
+          <t>yena0512@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>053-952-7172</t>
+          <t>0507-1339-0862</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로53길 14-2</t>
+          <t>대구광역시 북구 태암로5길 13-1 1층 102호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnYzxbxb</t>
+          <t>https://www.instagram.com/blinks_nail</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4172,7 +4168,7 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4181,13 +4177,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="R40" t="n">
-        <v>129</v>
+        <v>52</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,17 +4192,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1489887782</t>
+          <t>1424529823</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1489887782</t>
+          <t>https://m.place.naver.com/place/1424529823</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4218,12 +4214,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일,해주연</t>
+          <t>네일플루이</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>vely_sohee@naver.com</t>
+          <t>nailpluie@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -4231,17 +4227,17 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매전로4길 31 매천동753</t>
+          <t>대구광역시 북구 칠곡중앙대로110길 19 1층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_nzuin</t>
+          <t>https://blog.naver.com/nailpluie</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4251,7 +4247,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4262,22 +4258,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R41" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4286,17 +4282,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2041500566</t>
+          <t>1974701574</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041500566</t>
+          <t>https://m.place.naver.com/place/1974701574</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4308,34 +4304,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>비쥬네일</t>
+          <t>세니요미</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>thgus9800@naver.com</t>
+          <t>sennny@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>053-264-1130</t>
+          <t>0507-1471-0523</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로23길 2 동천골든프라자 1층</t>
+          <t>대구광역시 북구 대천로7길 6-16 1층 세니요미</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bijounail/</t>
+          <t>https://instabio.cc/4021506dbM8cU</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4356,7 +4352,7 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4365,13 +4361,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>26</v>
+        <v>265</v>
       </c>
       <c r="Q42" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="R42" t="n">
-        <v>71</v>
+        <v>350</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4380,17 +4376,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>36827317</t>
+          <t>1033303518</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36827317</t>
+          <t>https://m.place.naver.com/place/1033303518</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4402,29 +4398,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>온유뷰티</t>
+          <t>어제오늘네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nbc9896@naver.com</t>
+          <t>ksunmi88@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1433-0601</t>
+          <t>0507-1384-2440</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 30 상가동 102호 온유뷰티</t>
+          <t>대구광역시 북구 동암로 110 3층 어제오늘네일</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://instagram.com/on._u_beauty?igshid=YmMyMTA2M2Y=</t>
+          <t>https://www.instagram.com/yeto.nail2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4459,13 +4455,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>67</v>
+        <v>712</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="R43" t="n">
-        <v>77</v>
+        <v>891</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,17 +4470,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1391715445</t>
+          <t>1950980170</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391715445</t>
+          <t>https://m.place.naver.com/place/1950980170</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4492,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>그래비네일</t>
+          <t>공원옆네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>foryou48613@naver.com</t>
+          <t>hymizzang@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4509,12 +4505,12 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로18길 21 1층</t>
+          <t>대구광역시 북구 구암로21길 37 302동 208호</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail.park_</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4524,7 +4520,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4545,17 +4541,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4564,17 +4560,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1564740881</t>
+          <t>1948302097</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564740881</t>
+          <t>https://m.place.naver.com/place/1948302097</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4586,29 +4582,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>위티네일</t>
+          <t>코코수네일 복현점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jhjh9753@naver.com</t>
+          <t>alsxm777@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1438-6646</t>
+          <t>0507-1458-1158</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로9길 5 1층 위티네일</t>
+          <t>대구광역시 북구 대학로23길 10 2층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/witty.nail/</t>
+          <t>https://www.instagram.com/cocosu_nail/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4634,7 +4630,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4643,13 +4639,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="Q45" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="R45" t="n">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4658,17 +4654,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1037598797</t>
+          <t>1621329974</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037598797</t>
+          <t>https://m.place.naver.com/place/1621329974</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4680,25 +4676,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>유림네일&amp;뷰티</t>
+          <t>네일도 왁싱</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>iamhyojun02@naver.com</t>
+          <t>luv0e@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1395-1355</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매전로4길 10-93 1층(매천동)</t>
+          <t>대구광역시 북구 성북로 70 상가동 2층 210호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yurim._.nail</t>
+          <t>https://카카오톡오픈채팅을시작해보세요.링크를선택하면카카오톡이실행됩니다.네일도왁싱https//open.kakao.com/o/suNdDW4g</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4724,7 +4724,7 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>28</v>
+        <v>261</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="R46" t="n">
-        <v>29</v>
+        <v>380</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4748,17 +4748,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1328127606</t>
+          <t>1132125501</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1328127606</t>
+          <t>https://m.place.naver.com/place/1132125501</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4770,29 +4770,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>갓네일 &amp; 뷰티 대구역점</t>
+          <t>채희뷰티</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>god_nail_2000@naver.com</t>
+          <t>chaehee_beauty@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1432-2418</t>
+          <t>0507-1414-6681</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로 513 2층 202호 갓네일 대구역점</t>
+          <t>대구광역시 북구 동북로 247 상가동 2층 210호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/god_nail_8000</t>
+          <t>https://www.instagram.com/chaehee_beauty</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4818,7 +4818,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>431</v>
+        <v>524</v>
       </c>
       <c r="Q47" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="R47" t="n">
-        <v>519</v>
+        <v>575</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4842,17 +4842,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1364996819</t>
+          <t>1030745191</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364996819</t>
+          <t>https://m.place.naver.com/place/1030745191</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4864,29 +4864,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>뮤니크네일</t>
+          <t>한나네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>dahaepic@naver.com</t>
+          <t>raffinemoon@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1375-6408</t>
+          <t>0507-1337-5971</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로34길 16-19 1층 뮤니크네일</t>
+          <t>대구광역시 북구 대현남로2길 51 한나네일 1층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/munick_nail</t>
+          <t>https://www.instagram.com/hanna._.nail_</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4921,13 +4921,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q48" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="R48" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4936,17 +4936,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1805790304</t>
+          <t>1202246897</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805790304</t>
+          <t>https://m.place.naver.com/place/1202246897</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4958,29 +4958,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>모리앤네일</t>
+          <t>네일서아르</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>cute880201@naver.com</t>
+          <t>k_0608@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1362-4607</t>
+          <t>0507-1414-5027</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로 70 침산화성파크드림1008동 상가2층 222호</t>
+          <t>대구광역시 북구 침산로 246 1층 네일서아르</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_seoar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5006,22 +5006,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>8</v>
+        <v>248</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>9</v>
+        <v>254</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5030,17 +5030,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1109464508</t>
+          <t>1748877111</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109464508</t>
+          <t>https://m.place.naver.com/place/1748877111</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5052,29 +5052,25 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>푸키네일</t>
+          <t>바이느와르네일 칠성점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>pooky_nail@naver.com</t>
+          <t>din-dung@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0507-1379-9994</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 415 메가타운 7층, 예쁘디예쁘다 안</t>
+          <t>대구광역시 북구 중앙대로 513 대구오페라클래시아 2층 206호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pooky_nail</t>
+          <t>https://www.instagram.com/bynoir__nail_hj</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5109,13 +5105,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>480</v>
+        <v>130</v>
       </c>
       <c r="Q50" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="R50" t="n">
-        <v>532</v>
+        <v>236</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5124,17 +5120,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1189632296</t>
+          <t>1236270675</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189632296</t>
+          <t>https://m.place.naver.com/place/1236270675</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5146,29 +5142,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>에이무드뷰티</t>
+          <t>네일유</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sunsun900@naver.com</t>
+          <t>nail_u123@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1398-7711</t>
+          <t>0507-1343-1995</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로106길 2 2층</t>
+          <t>대구광역시 북구 구암로42길 10 101호 NAIL,U</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/amoodnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5178,7 +5174,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5199,17 +5195,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5214,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1257508634</t>
+          <t>1772663419</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257508634</t>
+          <t>https://m.place.naver.com/place/1772663419</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5240,29 +5236,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>하까네일&amp;래쉬</t>
+          <t>플로우네일케어</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bluefrog385@naver.com</t>
+          <t>frhlkfhkly3@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1394-0637</t>
+          <t>0507-1356-1202</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학남로 9 1층 하까네일&amp;래쉬</t>
+          <t>대구광역시 북구 연경지묘로 6 1층 108호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hakkanail</t>
+          <t>https://www.instagram.com/flow_nail_care/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5297,13 +5293,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,17 +5308,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1721951293</t>
+          <t>1644153139</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1721951293</t>
+          <t>https://m.place.naver.com/place/1644153139</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5334,30 +5330,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>마로네네일</t>
+          <t>엔케어센터 복현점 /내성발톱/발각질/무좀발톱/젤네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>huiyoung14@naver.com</t>
+          <t>ncarecenter@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1326-8241</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로2길 12 1층 오른쪽</t>
+          <t>대구광역시 북구 동북로 244 12층 1206호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_qxcBCxj</t>
+          <t>http://abalico.co.kr</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5378,7 +5378,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>114</v>
+        <v>704</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="R53" t="n">
-        <v>120</v>
+        <v>772</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5402,17 +5402,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1638307578</t>
+          <t>1956967552</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1638307578</t>
+          <t>https://m.place.naver.com/place/1956967552</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5424,39 +5424,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>멜리플루</t>
+          <t>푸키네일</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>hyojin092@naver.com</t>
+          <t>pooky_nail@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1388-1137</t>
+          <t>0507-1379-9994</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대동로 38 1층</t>
+          <t>대구광역시 북구 학정로 415 메가타운 7층, 예쁘디예쁘다 안</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYwXvAttF</t>
+          <t>https://www.instagram.com/pooky_nail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5472,7 +5472,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5481,13 +5481,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>100</v>
+        <v>483</v>
       </c>
       <c r="Q54" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="R54" t="n">
-        <v>123</v>
+        <v>535</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5496,17 +5496,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1330782670</t>
+          <t>1189632296</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330782670</t>
+          <t>https://m.place.naver.com/place/1189632296</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5518,29 +5518,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>아메리네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ksy3315@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1388-7339</t>
+          <t>0507-1395-1991</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태전로7길 10-17 두성타운상가 1층 네일리</t>
+          <t>대구광역시 북구 동화천로57길 13 카노빌 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailee_nr</t>
+          <t>https://www.instagram.com/ameri_nail</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5575,13 +5575,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>160</v>
+        <v>284</v>
       </c>
       <c r="Q55" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>167</v>
+        <v>288</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5590,17 +5590,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1928391317</t>
+          <t>1998879951</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928391317</t>
+          <t>https://m.place.naver.com/place/1998879951</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5612,29 +5612,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>올링네일</t>
+          <t>투모로우바이뷰티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>youngeun120@naver.com</t>
+          <t>yunsm04@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0507-1313-2265</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로24길 40 칠곡2차 영남타운 입구 옆 도로상가 올링네일</t>
+          <t>대구광역시 북구 칠곡중앙대로67길 20 1층</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/orling.nail?igsh=NnZkcjJjdzBhdXJz&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/tomorrow.by.beauty</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5669,13 +5665,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>23</v>
+        <v>585</v>
       </c>
       <c r="Q56" t="n">
-        <v>18</v>
+        <v>215</v>
       </c>
       <c r="R56" t="n">
-        <v>41</v>
+        <v>800</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5684,17 +5680,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1236901851</t>
+          <t>1006662497</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236901851</t>
+          <t>https://m.place.naver.com/place/1006662497</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5706,29 +5702,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>엔뉴아네일</t>
+          <t>알미네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>gkstnqls0858@naver.com</t>
+          <t>reina_99@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1480-4144</t>
+          <t>0507-1487-3656</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로22길 14 칠곡에덴타운 상가1층 엔뉴아네일</t>
+          <t>대구광역시 북구 칠곡중앙대로53길 24 1층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_n.newa?igsh=MW94emM2YnNsNndkNQ%3D%3D&amp;utm_source=qr</t>
+          <t>http://instagram.com/ar_my_nail</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5748,13 +5744,17 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5763,13 +5763,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R57" t="n">
-        <v>5</v>
+        <v>181</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5778,17 +5778,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1900044418</t>
+          <t>1406194751</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1900044418</t>
+          <t>https://m.place.naver.com/place/1406194751</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5800,29 +5800,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>몽뎅네일스튜디오</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>pk2hee@naver.com</t>
+          <t>ksy3315@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1314-6829</t>
+          <t>0507-1388-7339</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정동로 40 한라하우젠트2차 상가</t>
+          <t>대구광역시 북구 태전로7길 10-17 두성타운상가 1층 네일리</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mongdeng_nail</t>
+          <t>https://www.instagram.com/nailee_nr</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5857,13 +5857,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="Q58" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R58" t="n">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5872,17 +5872,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1973307356</t>
+          <t>1928391317</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973307356</t>
+          <t>https://m.place.naver.com/place/1928391317</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5894,34 +5894,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>네일바이비</t>
+          <t>미닛트 네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jin_a_diary@naver.com</t>
+          <t>dmsghk057@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1307-1576</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대학로23길 16-4 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로126길 7-12 105호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vBYPK</t>
+          <t>https://www.instagram.com/minute_nail_/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5942,7 +5938,7 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5951,13 +5947,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="Q59" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="R59" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5966,17 +5962,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1814661870</t>
+          <t>1139512492</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814661870</t>
+          <t>https://m.place.naver.com/place/1139512492</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5988,34 +5984,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>루미에르네일 연경점</t>
+          <t>더채온</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kneun93@naver.com</t>
+          <t>ameliepink@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1341-1267</t>
+          <t>0507-1337-9853</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경중앙로11길 33 우방아이유쉘 상가동 2층 208호</t>
+          <t>대구광역시 북구 침산로32길 11-7 2층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://instagram.com/lumierenail</t>
+          <t>http://pf.kakao.com/_rxfquX</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6036,7 +6032,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6045,13 +6041,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q60" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6060,17 +6056,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1857434697</t>
+          <t>2038014369</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1857434697</t>
+          <t>https://m.place.naver.com/place/2038014369</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6082,29 +6078,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일블링츠</t>
+          <t>뷰랩</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>mssjse@naver.com</t>
+          <t>miheynog@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1339-0862</t>
+          <t>0507-1417-9885</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태암로5길 13-1 1층 102호</t>
+          <t>대구광역시 북구 동천로 97 영남네오빌아트 106동 앞 상가</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/blinks_nail</t>
+          <t>https://www.instagram.com/viewlab</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6139,13 +6135,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>28</v>
+        <v>1388</v>
       </c>
       <c r="Q61" t="n">
-        <v>24</v>
+        <v>680</v>
       </c>
       <c r="R61" t="n">
-        <v>52</v>
+        <v>2068</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6154,17 +6150,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1424529823</t>
+          <t>1602365195</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1424529823</t>
+          <t>https://m.place.naver.com/place/1602365195</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6176,34 +6172,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>컨티뉴페이스</t>
+          <t>네일바이비</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>oncepromd@naver.com</t>
+          <t>jin_a_diary@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1358-0463</t>
+          <t>0507-1307-1576</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 434 대구읍내행복주택 상가 2층 205호 &lt;지하주차무료&gt;</t>
+          <t>대구광역시 북구 대학로23길 16-4 1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/continewface_nail?igsh=YWhvMzgweWY2Zmhp</t>
+          <t>http://pf.kakao.com/_vBYPK</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6224,7 +6220,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6233,13 +6229,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>767</v>
+        <v>27</v>
       </c>
       <c r="Q62" t="n">
-        <v>881</v>
+        <v>33</v>
       </c>
       <c r="R62" t="n">
-        <v>1648</v>
+        <v>60</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6248,17 +6244,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1991303123</t>
+          <t>1814661870</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991303123</t>
+          <t>https://m.place.naver.com/place/1814661870</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6270,34 +6266,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>가비뷰티</t>
+          <t>네일리즈</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>dadalover0407@naver.com</t>
+          <t>taehana0426@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1315-8548</t>
+          <t>0507-1392-4881</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태전로3길 17-1 1층 (태전동)</t>
+          <t>대구광역시 북구 구암로39길 18-3 1층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_evbSxj</t>
+          <t>https://www.instagram.com/nail_rizz_</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6318,7 +6314,7 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6327,13 +6323,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6342,17 +6338,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1054977148</t>
+          <t>1403873554</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054977148</t>
+          <t>https://m.place.naver.com/place/1403873554</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6364,29 +6360,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>뷰티스공간</t>
+          <t>컨티뉴페이스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>jwifem@naver.com</t>
+          <t>oncepromd@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1347-8607</t>
+          <t>0507-1358-0463</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 100 오페라삼정 그린코아더베스트 상가동 107호</t>
+          <t>대구광역시 북구 칠곡중앙대로 434 대구읍내행복주택 상가 2층 205호 &lt;지하주차무료&gt;</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_gongan</t>
+          <t>https://www.instagram.com/continewface_nail?igsh=YWhvMzgweWY2Zmhp</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6421,13 +6417,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>113</v>
+        <v>767</v>
       </c>
       <c r="Q64" t="n">
-        <v>51</v>
+        <v>881</v>
       </c>
       <c r="R64" t="n">
-        <v>164</v>
+        <v>1648</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6436,17 +6432,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1680122870</t>
+          <t>1991303123</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1680122870</t>
+          <t>https://m.place.naver.com/place/1991303123</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6458,34 +6454,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>프롬퀸 네일</t>
+          <t>마이영네일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>promqueen0912@naver.com</t>
+          <t>yujinlee10@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1396-5688</t>
+          <t>053-952-7172</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로77길 31-3</t>
+          <t>대구광역시 북구 동북로53길 14-2</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/promqueen0912</t>
+          <t>http://pf.kakao.com/_xnYzxbxb</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6495,7 +6491,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6515,13 +6511,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>259</v>
+        <v>120</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="R65" t="n">
-        <v>262</v>
+        <v>131</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6530,17 +6526,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1449308514</t>
+          <t>1489887782</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1449308514</t>
+          <t>https://m.place.naver.com/place/1489887782</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6552,29 +6548,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>아메리네일</t>
+          <t>그리다네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>gridanail2@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1395-1991</t>
+          <t>0507-1369-9356</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동화천로57길 13 카노빌 1층</t>
+          <t>대구광역시 북구 대동로1길 75 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ameri_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6584,7 +6580,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6605,17 +6601,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>284</v>
+        <v>35</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="R66" t="n">
-        <v>288</v>
+        <v>63</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6624,17 +6620,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1998879951</t>
+          <t>1281503156</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1998879951</t>
+          <t>https://m.place.naver.com/place/1281503156</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6646,29 +6642,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일존 침산점</t>
+          <t>네일다니</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vgomugomv@naver.com</t>
+          <t>nail_dani@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1368-9413</t>
+          <t>0507-1326-6288</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 93 칠성이마트 지하1층</t>
+          <t>대구광역시 북구 태암남로11길 28-1 네일다니</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/nail_dani</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6678,12 +6674,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6694,22 +6690,22 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>36</v>
+        <v>414</v>
       </c>
       <c r="Q67" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="R67" t="n">
-        <v>46</v>
+        <v>438</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6718,17 +6714,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1659658078</t>
+          <t>1058398706</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1659658078</t>
+          <t>https://m.place.naver.com/place/1058398706</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6740,29 +6736,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>네일리즈</t>
+          <t>에이무드뷰티</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ssarra1234@naver.com</t>
+          <t>sunsun900@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1392-4881</t>
+          <t>0507-1398-7711</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로39길 18-3 1층</t>
+          <t>대구광역시 북구 중앙대로106길 2 2층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_rizz_</t>
+          <t>https://www.instagram.com/amoodnail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6797,13 +6793,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="R68" t="n">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6812,17 +6808,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1403873554</t>
+          <t>1257508634</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1403873554</t>
+          <t>https://m.place.naver.com/place/1257508634</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6834,34 +6830,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일서아르</t>
+          <t>네일105 복현 본점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>k_0608@naver.com</t>
+          <t>nail105@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1414-5027</t>
+          <t>0507-1324-0222</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 246 1층 네일서아르</t>
+          <t>대구광역시 북구 동북로 223 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_seoar</t>
+          <t>http://www.instagram.com/nail.105</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6871,7 +6867,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6882,7 +6878,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6891,13 +6887,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>248</v>
+        <v>1340</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="R69" t="n">
-        <v>254</v>
+        <v>1380</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6906,17 +6902,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1748877111</t>
+          <t>1205043851</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748877111</t>
+          <t>https://m.place.naver.com/place/1205043851</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6928,34 +6924,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>네일라쥬르</t>
+          <t>모카네일</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>dkenl0103@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1371-0767</t>
+          <t>0507-1446-1569</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로 223</t>
+          <t>대구광역시 북구 학정동로13길 3 1층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lasure_nail</t>
+          <t>http://pf.kakao.com/_xcubwn</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6976,7 +6972,7 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6985,13 +6981,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>38</v>
+        <v>494</v>
       </c>
       <c r="Q70" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="R70" t="n">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7000,17 +6996,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1303390693</t>
+          <t>1744601857</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303390693</t>
+          <t>https://m.place.naver.com/place/1744601857</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7022,29 +7018,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>코코수네일 복현점</t>
+          <t>위티네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>alsxm777@naver.com</t>
+          <t>jhjh9753@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1458-1158</t>
+          <t>0507-1438-6646</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대학로23길 10 2층</t>
+          <t>대구광역시 북구 성북로9길 5 1층 위티네일</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cocosu_nail/</t>
+          <t>https://www.instagram.com/witty.nail/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7070,7 +7066,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7079,13 +7075,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="Q71" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="R71" t="n">
-        <v>173</v>
+        <v>50</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7094,17 +7090,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1621329974</t>
+          <t>1037598797</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1621329974</t>
+          <t>https://m.place.naver.com/place/1037598797</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7116,29 +7112,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>한나네일</t>
+          <t>뷰티스공간</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>raffinemoon@naver.com</t>
+          <t>jwifem@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1337-5971</t>
+          <t>0507-1347-8607</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대현남로2길 51 한나네일 1층</t>
+          <t>대구광역시 북구 침산로 100 오페라삼정 그린코아더베스트 상가동 107호</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hanna._.nail_</t>
+          <t>https://www.instagram.com/beauty_gongan</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7173,13 +7169,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="Q72" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="R72" t="n">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7188,17 +7184,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1202246897</t>
+          <t>1680122870</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202246897</t>
+          <t>https://m.place.naver.com/place/1680122870</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7210,29 +7206,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>에이네일</t>
+          <t>설레는 네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>share_img@naver.com</t>
+          <t>woori8999@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1489-5668</t>
+          <t>0507-1460-0172</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 426 하나은행건물 3층</t>
+          <t>대구광역시 북구 동북로 131 양우내안에아파트 상가 1층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.nail0</t>
+          <t>https://www.instagram.com/sullem_mn</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7267,13 +7263,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="Q73" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="R73" t="n">
-        <v>41</v>
+        <v>271</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7282,17 +7278,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1014010899</t>
+          <t>1264344506</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1014010899</t>
+          <t>https://m.place.naver.com/place/1264344506</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7304,29 +7300,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>그리다네일</t>
+          <t>올링네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>gridanail2@naver.com</t>
+          <t>youngeun120@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1369-9356</t>
+          <t>0507-1313-2265</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대동로1길 75 1층</t>
+          <t>대구광역시 북구 팔거천동로24길 40 칠곡2차 영남타운 입구 옆 도로상가 올링네일</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/orling.nail?igsh=NnZkcjJjdzBhdXJz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7336,7 +7332,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7357,17 +7353,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="Q74" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="R74" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7376,17 +7372,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1281503156</t>
+          <t>1236901851</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281503156</t>
+          <t>https://m.place.naver.com/place/1236901851</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7398,25 +7394,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>아띠네일</t>
+          <t>네일다방</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>attinail_@naver.com</t>
+          <t>moorai79@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1481-2286</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호국로57길 31-12 1층 아띠네일</t>
+          <t>대구광역시 북구 한강로6길 13 밸류스퀘어빌딩 1층 102호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_dabang_?igsh=cGY3NmcxaWl6ZG9x</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7447,17 +7447,17 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7466,17 +7466,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1088451483</t>
+          <t>1515988410</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088451483</t>
+          <t>https://m.place.naver.com/place/1515988410</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7488,30 +7488,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>바이느와르네일 칠성점</t>
+          <t>노이브</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>hhoney0824@naver.com</t>
+          <t>rhgustn911@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1374-0639</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로 513 대구오페라클래시아 2층 206호</t>
+          <t>대구광역시 북구 서변로 88 116동 105호 노이브네일</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bynoir__nail_hj</t>
+          <t>http://pf.kakao.com/_ettmG/chat</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -7532,7 +7536,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7541,13 +7545,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>231</v>
+        <v>1</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7556,17 +7560,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1236270675</t>
+          <t>1657841286</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236270675</t>
+          <t>https://m.place.naver.com/place/1657841286</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/북구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/북구_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>갓네일 &amp; 뷰티 대구역점</t>
+          <t>한나네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>god_nail_2000@naver.com</t>
+          <t>raffinemoon@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1432-2418</t>
+          <t>0507-1337-5971</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로 513 2층 202호 갓네일 대구역점</t>
+          <t>대구광역시 북구 대현남로2길 51 한나네일 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/god_nail_8000</t>
+          <t>https://www.instagram.com/hanna._.nail_</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>442</v>
+        <v>65</v>
       </c>
       <c r="Q2" t="n">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="R2" t="n">
-        <v>535</v>
+        <v>100</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1364996819</t>
+          <t>1202246897</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364996819</t>
+          <t>https://m.place.naver.com/place/1202246897</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,25 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>모제스튜디오</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>어제오늘네일</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ksunmi88@naver.com</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1360-2673</t>
+          <t>0507-1384-2440</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로31길 1 1층</t>
+          <t>대구광역시 북구 동암로 110 3층 어제오늘네일</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moje_nailstudio?igsh=emdzbm4xMmJhd2dl</t>
+          <t>https://www.instagram.com/yeto.nail2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -702,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -711,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>910</v>
+        <v>712</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>184</v>
       </c>
       <c r="R3" t="n">
-        <v>915</v>
+        <v>896</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1258515201</t>
+          <t>1950980170</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258515201</t>
+          <t>https://m.place.naver.com/place/1950980170</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -748,25 +752,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한나네일</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>미닛트 네일</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dmsghk057@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1337-5971</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대현남로2길 51 한나네일 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로126길 7-12 105호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hanna._.nail_</t>
+          <t>https://www.instagram.com/minute_nail_/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -801,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -816,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1202246897</t>
+          <t>1139512492</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202246897</t>
+          <t>https://m.place.naver.com/place/1139512492</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -838,29 +842,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일다니</t>
+          <t>네일블링츠</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nail_dani@naver.com</t>
+          <t>yena0512@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1326-6288</t>
+          <t>0507-1339-0862</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태암남로11길 28-1 네일다니</t>
+          <t>대구광역시 북구 태암로5길 13-1 1층 102호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_dani</t>
+          <t>https://www.instagram.com/blinks_nail</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -875,7 +879,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -886,7 +890,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -895,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>414</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="n">
         <v>24</v>
       </c>
       <c r="R5" t="n">
-        <v>438</v>
+        <v>52</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1058398706</t>
+          <t>1424529823</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058398706</t>
+          <t>https://m.place.naver.com/place/1424529823</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -932,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>화야네일앤뷰티</t>
+          <t>플로우네일케어</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sbsb100488@naver.com</t>
+          <t>frhlkfhkly3@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1319-6498</t>
+          <t>0507-1356-1202</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로35길 4 1층</t>
+          <t>대구광역시 북구 연경지묘로 6 1층 108호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hwaya_beauty</t>
+          <t>https://www.instagram.com/flow_nail_care/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +984,7 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -989,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="Q6" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>311</v>
+        <v>122</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1283528001</t>
+          <t>1644153139</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283528001</t>
+          <t>https://m.place.naver.com/place/1644153139</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1026,25 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>위티네일</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>뷰랩</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>miheynog@naver.com</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1438-6646</t>
+          <t>0507-1417-9885</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로9길 5 1층 위티네일</t>
+          <t>대구광역시 북구 동천로 97 영남네오빌아트 106동 앞 상가</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/witty.nail/</t>
+          <t>https://www.instagram.com/viewlab</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1070,7 +1078,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1079,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>20</v>
+        <v>1390</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>681</v>
       </c>
       <c r="R7" t="n">
-        <v>50</v>
+        <v>2071</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1094,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1037598797</t>
+          <t>1602365195</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037598797</t>
+          <t>https://m.place.naver.com/place/1602365195</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1116,29 +1124,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일바다</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>kiwi10041010@naver.com</t>
-        </is>
-      </c>
+          <t>네일서아르</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1317-2364</t>
+          <t>0507-1414-5027</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로108길 21 1층 네일바다</t>
+          <t>대구광역시 북구 침산로 246 1층 네일서아르</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.bada</t>
+          <t>https://www.instagram.com/nail_seoar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1164,7 +1168,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1173,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>249</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>255</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1188,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1756678430</t>
+          <t>1748877111</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756678430</t>
+          <t>https://m.place.naver.com/place/1748877111</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1210,35 +1214,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>세니요미</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>은뷰티</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>tajoa19@naver.com</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1471-0523</t>
+          <t>0507-1366-9360</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로7길 6-16 1층 세니요미</t>
+          <t>대구광역시 북구 침산로22길 5 102동 112호 은뷰티</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://instabio.cc/4021506dbM8cU</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1254,22 +1262,22 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>265</v>
+        <v>49</v>
       </c>
       <c r="Q9" t="n">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="R9" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1278,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1033303518</t>
+          <t>2094752142</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033303518</t>
+          <t>https://m.place.naver.com/place/2094752142</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1300,25 +1308,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>그리다네일</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>네일도 왁싱</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>luv0e@naver.com</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1369-9356</t>
+          <t>0507-1395-1355</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대동로1길 75 1층</t>
+          <t>대구광역시 북구 성북로 70 상가동 2층 210호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://카카오톡오픈채팅을시작해보세요.링크를선택하면카카오톡이실행됩니다.네일도왁싱https//open.kakao.com/o/suNdDW4g</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1328,7 +1340,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1344,22 +1356,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>262</v>
       </c>
       <c r="Q10" t="n">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="R10" t="n">
-        <v>63</v>
+        <v>381</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1368,17 +1380,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1281503156</t>
+          <t>1132125501</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281503156</t>
+          <t>https://m.place.naver.com/place/1132125501</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1390,29 +1402,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엔뉴아네일</t>
+          <t>민이네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gkstnqls0858@naver.com</t>
+          <t>lee_dormery@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1480-4144</t>
+          <t>0507-1405-3361</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로22길 14 칠곡에덴타운 상가1층 엔뉴아네일</t>
+          <t>대구광역시 북구 대동로 50 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_n.newa?igsh=MW94emM2YnNsNndkNQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/_mi.ni_nail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1450,10 +1462,10 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1462,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1900044418</t>
+          <t>1867922573</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1900044418</t>
+          <t>https://m.place.naver.com/place/1867922573</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1484,30 +1496,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>꼬미네일</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>네일플루이</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>nailpluie@naver.com</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1398-9513</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 북구 한강로6길 7-4 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로110길 19 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/CUdrackv2Uh/?utm_medium=copy_link</t>
+          <t>https://blog.naver.com/nailpluie</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1537,13 +1549,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1552,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1695465470</t>
+          <t>1974701574</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695465470</t>
+          <t>https://m.place.naver.com/place/1974701574</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1574,21 +1586,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>낭만네일</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>코코수네일 복현점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>alsxm777@naver.com</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1458-1158</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로31길 11</t>
+          <t>대구광역시 북구 대학로23길 10 2층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>http://nangmannail.com</t>
+          <t>https://www.instagram.com/cocosu_nail/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1623,32 +1643,5930 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>13</v>
+      </c>
+      <c r="R13" t="n">
+        <v>173</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1621329974</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1621329974</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>네일디보티</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1022eunji@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>053-351-7622</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀 상가106호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail_devotee</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>18</v>
+      </c>
+      <c r="R14" t="n">
+        <v>26</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>37604636</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37604636</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>살롱드302</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hanseon216@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1366-7799</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠곡중앙대로 434 2층 206호 살롱드302</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://linkfly.to/70627DEJDap</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>395</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>11</v>
+      </c>
+      <c r="R15" t="n">
+        <v>406</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1472140745</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1472140745</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>아띠네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>attinail_@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 호국로57길 31-12 1층 아띠네일</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>15</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1088451483</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1088451483</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>네일105 복현 본점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>nail105@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1324-0222</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 223 1층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/nail.105</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>1342</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>40</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1382</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1205043851</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1205043851</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>에이네일</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>hajw0129@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1489-5668</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정로 426 하나은행건물 3층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a.nail0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>38</v>
+      </c>
+      <c r="R18" t="n">
+        <v>40</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1014010899</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1014010899</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>온유뷰티</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>nhbnhb05@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1433-0601</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠성남로 30 상가동 102호 온유뷰티</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://instagram.com/on._u_beauty?igshid=YmMyMTA2M2Y=</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10</v>
+      </c>
+      <c r="R19" t="n">
+        <v>79</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1391715445</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1391715445</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>에이무드뷰티</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sunsun900@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1398-7711</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 중앙대로106길 2 2층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/amoodnail</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>16</v>
+      </c>
+      <c r="R20" t="n">
+        <v>54</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1257508634</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1257508634</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>가비뷰티</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>dadalover0407@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1315-8548</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 태전로3길 17-1 1층 (태전동)</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_evbSxj</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>15</v>
+      </c>
+      <c r="R21" t="n">
+        <v>82</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1054977148</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1054977148</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>네일리</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ysbfly@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1388-7339</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 태전로7길 10-17 두성타운상가 1층 네일리</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nailee_nr</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>161</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>168</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1928391317</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928391317</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>네일라쥬르</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dkenl0103@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1371-0767</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 팔달로 223</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lasure_nail</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>44</v>
+      </c>
+      <c r="R23" t="n">
+        <v>82</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1303390693</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303390693</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>마이영네일</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>yujinlee10@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>053-952-7172</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로53길 14-2</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xnYzxbxb</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>11</v>
+      </c>
+      <c r="R24" t="n">
+        <v>131</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>1489887782</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1489887782</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>구르미네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>gurmi_nail_240624@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1344-0696</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠곡중앙대로116길 24 1층 구르미네일</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>http://instagram.com/9reumi_nail</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>24</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1928346749</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1928346749</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>유어메리뷰티</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>multtang1@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1378-9783</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 복현로20길 2 1층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_mBAAn</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>157</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>159</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1050332478</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1050332478</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>화야네일앤뷰티</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sbsb100488@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1319-6498</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 팔달로35길 4 1층</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/hwaya_beauty</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>83</v>
+      </c>
+      <c r="R27" t="n">
+        <v>311</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1283528001</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1283528001</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>뮤니크네일</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>meohaseyo@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1375-6408</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 팔거천동로34길 16-19 1층 뮤니크네일</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/munick_nail</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>8</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1805790304</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1805790304</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>더채온</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ameliepink@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1337-9853</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로32길 11-7 2층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_rxfquX</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>10</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2038014369</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2038014369</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>엔케어센터 복현점 /내성발톱/발각질/무좀발톱/젤네일</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ncarecenter@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1326-8241</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 244 12층 1206호</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>http://abalico.co.kr</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>706</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>67</v>
+      </c>
+      <c r="R30" t="n">
+        <v>773</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1956967552</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1956967552</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>멜리플루</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sycep@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1388-1137</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 대동로 38 1층</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://toss.place/_lb/TYwXvAttF</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>23</v>
+      </c>
+      <c r="R31" t="n">
+        <v>125</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1330782670</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1330782670</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>시월의 네일</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>chltys1@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1368-1165</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 중앙대로105길 22 시월의 네일</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_DwWvb</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>14</v>
+      </c>
+      <c r="R32" t="n">
         <v>25</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>1443846421</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1443846421</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>푸키네일</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>pooky_nail@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1379-9994</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정로 415 메가타운 7층, 예쁘디예쁘다 안</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pooky_nail</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>483</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>52</v>
+      </c>
+      <c r="R33" t="n">
+        <v>535</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1189632296</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1189632296</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>위티네일</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>jhjh9753@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1438-6646</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 성북로9길 5 1층 위티네일</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/witty.nail/</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>30</v>
+      </c>
+      <c r="R34" t="n">
+        <v>50</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1037598797</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1037598797</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nail Vivienne</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>spotv_sports@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1352-1254</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 한강로 72-1 비비엔느네일</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>15</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1234676332</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1234676332</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>네일유</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nail_u123@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1343-1995</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 구암로42길 10 101호 NAIL,U</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1772663419</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1772663419</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>뷰티스공간</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jwifem@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1347-8607</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 100 오페라삼정 그린코아더베스트 상가동 107호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/beauty_gongan</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>51</v>
+      </c>
+      <c r="R37" t="n">
+        <v>164</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1680122870</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1680122870</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>몽뎅네일스튜디오</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>pk2hee@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1314-6829</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정동로 40 한라하우젠트2차 상가</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mongdeng_nail</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>170</v>
+      </c>
+      <c r="Q38" t="n">
         <v>11</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R38" t="n">
+        <v>181</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1973307356</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1973307356</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>데이즈네일</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>pungkang82@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1355-6444</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 구암로65길 52 3층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/daze.nail_/</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>28</v>
+      </c>
+      <c r="R39" t="n">
+        <v>31</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1089749071</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1089749071</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>네일드민</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>alswl990324@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1487-8770</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 관음중앙로22길 5 1층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_pwxnnn</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>9</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1595309498</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1595309498</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>네일피오나</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>cjrut2674@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1364-8481</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 매전로4길 22 1층 네일 피오나</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_piona</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>5</v>
+      </c>
+      <c r="R41" t="n">
+        <v>96</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1410565139</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1410565139</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>모리앤네일</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>whatever21@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1362-4607</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 성북로 70 침산화성파크드림1008동 상가2층 222호</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>9</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1109464508</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1109464508</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>모제스튜디오</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>possam-@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1360-2673</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산남로31길 1 1층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/moje_nailstudio?igsh=emdzbm4xMmJhd2dl</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>913</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>918</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1258515201</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1258515201</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>오아이뷰티</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>mycutegod@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1339-2823</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠성남로 70 근린생활시설 207호(2층)</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/oi_b.room</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>21</v>
+      </c>
+      <c r="R44" t="n">
+        <v>31</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1302335033</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1302335033</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>갓네일 &amp; 뷰티 대구역점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>god_nail_2000@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1432-2418</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 중앙대로 513 2층 202호 갓네일 대구역점</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/god_nail_8000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>449</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>94</v>
+      </c>
+      <c r="R45" t="n">
+        <v>543</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1364996819</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1364996819</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>하까네일&amp;래쉬</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>bluefrog385@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1394-0637</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학남로 9 1층 하까네일&amp;래쉬</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hakkanail</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>138</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1721951293</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1721951293</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>네일다니</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>nail_dani@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1326-6288</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 태암남로11길 28-1 네일다니</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nail_dani</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>414</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>24</v>
+      </c>
+      <c r="R47" t="n">
+        <v>438</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1058398706</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1058398706</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>그래비네일</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>foryou48613@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 대천로18길 21 1층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4</v>
+      </c>
+      <c r="R48" t="n">
+        <v>47</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1564740881</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1564740881</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>아메리네일</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>hankyuldata@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1395-1991</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동화천로57길 13 카노빌 1층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ameri_nail</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>285</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>4</v>
+      </c>
+      <c r="R49" t="n">
+        <v>289</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1998879951</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1998879951</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>올링네일</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>youngeun120@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1313-2265</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 팔거천동로24길 40 칠곡2차 영남타운 입구 옆 도로상가 올링네일</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/orling.nail?igsh=NnZkcjJjdzBhdXJz&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>18</v>
+      </c>
+      <c r="R50" t="n">
+        <v>41</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1236901851</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236901851</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>루미포레네일</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>uilll77@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1377-3829</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 163 202동 107호</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xhpAyn</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>67</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>2023409739</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2023409739</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>네일리즈</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>taehana0426@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1392-4881</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 구암로39길 18-3 1층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_rizz_</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>3</v>
+      </c>
+      <c r="R52" t="n">
+        <v>75</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1403873554</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1403873554</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>레몬 네일</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gorgeous_na_@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1430-2811</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 호국로43길 27 . 상가 1층 북측</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lemon___nail</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>18</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1070857201</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070857201</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>그리다네일</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>gridanail2@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1369-9356</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 대동로1길 75 1층</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>28</v>
+      </c>
+      <c r="R54" t="n">
+        <v>63</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1281503156</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1281503156</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>레푸스 칠곡점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>hjw8125@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1319-8125</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠곡중앙대로 244 3층</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hjw8125</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>356</v>
+      </c>
+      <c r="R55" t="n">
+        <v>507</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1036282232</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1036282232</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>비니뷰티샵</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>cllctmmt@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1423-7769</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정로109길 12 1층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s3QEI0nh</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q56" t="n">
         <v>36</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1055429676</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1055429676</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-25</t>
+      <c r="R56" t="n">
+        <v>50</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1794625110</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1794625110</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>에즈인뷰티</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>aboutdearme@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1321-7029</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로 246 1층 에즈인뷰티</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/az.in_b/</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>14</v>
+      </c>
+      <c r="R57" t="n">
+        <v>112</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1797804703</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1797804703</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>채희뷰티 침산점</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>chaehyejung1@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1359-0318</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 고성로 142 3층 301호</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chaehee_beauty_sol</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2</v>
+      </c>
+      <c r="R58" t="n">
+        <v>10</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>2020966033</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2020966033</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>소이네일</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>bin1549@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1352-3577</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 옥산로 95 1층 114호</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/soee.nail?igsh=c3NqcjZzMWZsZWk1&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>2045962730</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2045962730</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>알미네일</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1487-3656</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠곡중앙대로53길 24 1층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>http://instagram.com/ar_my_nail</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>168</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>13</v>
+      </c>
+      <c r="R60" t="n">
+        <v>181</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1406194751</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1406194751</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>네일 르 마지</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>hihy925@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1360-8063</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀오피스텔 상가 2층 201호</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_lemazi</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>8</v>
+      </c>
+      <c r="R61" t="n">
+        <v>193</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1295693572</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1295693572</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>네일바다</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>kiwi10041010@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1317-2364</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠곡중앙대로108길 21 1층 네일바다</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>http://instagram.com/nail.bada</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1756678430</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1756678430</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>이든네일</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ansdkfma0822@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0507-1381-2723</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 고성북로 34 오페라트루엘시민의숲 상가 201호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/edeun_nail</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>160</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2</v>
+      </c>
+      <c r="R63" t="n">
+        <v>162</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1221641229</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1221641229</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>바이느와르네일 칠성점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0722kk_@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 중앙대로 513 대구오페라클래시아 2층 206호</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bynoir__nail_hj</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>107</v>
+      </c>
+      <c r="R64" t="n">
+        <v>238</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1236270675</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236270675</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>네일,해주연</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>vely_sohee@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 매전로4길 31 매천동753</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_nzuin</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>88</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>2041500566</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2041500566</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>리리네일</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>hime_s2@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1379-6902</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정동로 76 1층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hime_s2</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>160</v>
+      </c>
+      <c r="R66" t="n">
+        <v>291</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1536988597</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1536988597</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>네일바이비</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>jin_a_diary@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1307-1576</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 대학로23길 16-4 1층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_vBYPK</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>33</v>
+      </c>
+      <c r="R67" t="n">
+        <v>60</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1814661870</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1814661870</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>컨티뉴페이스</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>oncepromd@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1358-0463</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠곡중앙대로 434 대구읍내행복주택 상가 2층 205호 &lt;지하주차무료&gt;</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/continewface_nail?igsh=YWhvMzgweWY2Zmhp</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>769</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>881</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1650</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1991303123</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1991303123</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>애몽</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>emong0902@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1332-4233</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 매전로 50-14 1층, 애몽</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_aemong</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>554</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>34</v>
+      </c>
+      <c r="R69" t="n">
+        <v>588</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1174913259</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1174913259</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>세니요미</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sennny@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1471-0523</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 대천로7길 6-16 1층 세니요미</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://instabio.cc/4021506dbM8cU</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>85</v>
+      </c>
+      <c r="R70" t="n">
+        <v>350</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>1033303518</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1033303518</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>공원옆네일</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>hymizzang@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 구암로21길 37 302동 208호</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail.park_</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3</v>
+      </c>
+      <c r="R71" t="n">
+        <v>94</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1948302097</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1948302097</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>채희뷰티</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>chaehee_beauty@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1414-6681</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 247 상가동 2층 210호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chaehee_beauty</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>527</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>51</v>
+      </c>
+      <c r="R72" t="n">
+        <v>578</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1030745191</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1030745191</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>투모로우바이뷰티</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>yunsm04@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 칠곡중앙대로67길 20 1층</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tomorrow.by.beauty</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>586</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>215</v>
+      </c>
+      <c r="R73" t="n">
+        <v>801</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1006662497</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1006662497</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>네일수미</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>rawith0411@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1362-2568</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 성북로 8 1F 18호</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_SIxixlxj</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>5</v>
+      </c>
+      <c r="R74" t="n">
+        <v>146</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1461190392</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1461190392</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>모카네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>daonnail0305@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1446-1569</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 학정동로13길 3 1층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_xcubwn</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>499</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>12</v>
+      </c>
+      <c r="R75" t="n">
+        <v>511</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1744601857</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1744601857</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>설레는 네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>daonnail0305@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1460-0172</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 동북로 131 양우내안에아파트 상가 1층</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sullem_mn</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>253</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>21</v>
+      </c>
+      <c r="R76" t="n">
+        <v>274</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1264344506</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1264344506</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/북구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/북구_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1127,7 +1127,11 @@
           <t>네일서아르</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>k_0608@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
@@ -1219,7 +1223,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tajoa19@naver.com</t>
+          <t>bazilamy@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>luv0e@naver.com</t>
+          <t>vanhada_beauty@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -2616,34 +2620,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>마이영네일</t>
+          <t>아우라모이네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>yujinlee10@naver.com</t>
+          <t>nailhiro@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>053-952-7172</t>
+          <t>0507-1365-8361</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로53길 14-2</t>
+          <t>대구광역시 북구 성북로 70 상가동 212호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnYzxbxb</t>
+          <t>https://blog.naver.com/nailhiro</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2653,7 +2657,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2673,13 +2677,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>120</v>
+        <v>13</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,12 +2692,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1489887782</t>
+          <t>2020256127</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1489887782</t>
+          <t>https://m.place.naver.com/place/2020256127</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2710,34 +2714,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>구르미네일</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>gurmi_nail_240624@naver.com</t>
-        </is>
-      </c>
+          <t>마이영네일</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1344-0696</t>
+          <t>053-952-7172</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로116길 24 1층 구르미네일</t>
+          <t>대구광역시 북구 동북로53길 14-2</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://instagram.com/9reumi_nail</t>
+          <t>http://pf.kakao.com/_xnYzxbxb</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2758,7 +2758,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2767,13 +2767,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R25" t="n">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1928346749</t>
+          <t>1489887782</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928346749</t>
+          <t>https://m.place.naver.com/place/1489887782</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2804,34 +2804,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>유어메리뷰티</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>multtang1@naver.com</t>
-        </is>
-      </c>
+          <t>구르미네일</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1378-9783</t>
+          <t>0507-1344-0696</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로20길 2 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로116길 24 1층 구르미네일</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_mBAAn</t>
+          <t>http://instagram.com/9reumi_nail</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2852,7 +2848,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2861,13 +2857,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,12 +2872,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1050332478</t>
+          <t>1928346749</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050332478</t>
+          <t>https://m.place.naver.com/place/1928346749</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2898,34 +2894,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>화야네일앤뷰티</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>sbsb100488@naver.com</t>
-        </is>
-      </c>
+          <t>유어메리뷰티</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1319-6498</t>
+          <t>0507-1378-9783</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로35길 4 1층</t>
+          <t>대구광역시 북구 복현로20길 2 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hwaya_beauty</t>
+          <t>http://pf.kakao.com/_mBAAn</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2955,13 +2947,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>228</v>
+        <v>157</v>
       </c>
       <c r="Q27" t="n">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>311</v>
+        <v>159</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,12 +2962,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1283528001</t>
+          <t>1050332478</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283528001</t>
+          <t>https://m.place.naver.com/place/1050332478</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2992,29 +2984,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>뮤니크네일</t>
+          <t>화야네일앤뷰티</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>meohaseyo@naver.com</t>
+          <t>sbsb100488@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1375-6408</t>
+          <t>0507-1319-6498</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로34길 16-19 1층 뮤니크네일</t>
+          <t>대구광역시 북구 팔달로35길 4 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/munick_nail</t>
+          <t>http://www.instagram.com/hwaya_beauty</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3040,7 +3032,7 @@
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3049,13 +3041,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="Q28" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="R28" t="n">
-        <v>8</v>
+        <v>311</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,12 +3056,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1805790304</t>
+          <t>1283528001</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805790304</t>
+          <t>https://m.place.naver.com/place/1283528001</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3086,34 +3078,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>더채온</t>
+          <t>뮤니크네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ameliepink@naver.com</t>
+          <t>meohaseyo@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1337-9853</t>
+          <t>0507-1375-6408</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로32길 11-7 2층</t>
+          <t>대구광역시 북구 팔거천동로34길 16-19 1층 뮤니크네일</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rxfquX</t>
+          <t>https://www.instagram.com/munick_nail</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3134,7 +3126,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3143,13 +3135,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,12 +3150,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2038014369</t>
+          <t>1805790304</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038014369</t>
+          <t>https://m.place.naver.com/place/1805790304</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3180,34 +3172,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>엔케어센터 복현점 /내성발톱/발각질/무좀발톱/젤네일</t>
+          <t>더채온</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ncarecenter@naver.com</t>
+          <t>ameliepink@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1326-8241</t>
+          <t>0507-1337-9853</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 12층 1206호</t>
+          <t>대구광역시 북구 침산로32길 11-7 2층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://abalico.co.kr</t>
+          <t>http://pf.kakao.com/_rxfquX</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3228,7 +3220,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3237,13 +3229,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>706</v>
+        <v>9</v>
       </c>
       <c r="Q30" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>773</v>
+        <v>10</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3252,12 +3244,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1956967552</t>
+          <t>2038014369</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956967552</t>
+          <t>https://m.place.naver.com/place/2038014369</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3274,39 +3266,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>멜리플루</t>
+          <t>엔케어센터 복현점 /내성발톱/발각질/무좀발톱/젤네일</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sycep@naver.com</t>
+          <t>ncarecenter@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1388-1137</t>
+          <t>0507-1326-8241</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대동로 38 1층</t>
+          <t>대구광역시 북구 동북로 244 12층 1206호</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYwXvAttF</t>
+          <t>http://abalico.co.kr</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3322,7 +3314,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3331,13 +3323,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>102</v>
+        <v>706</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="R31" t="n">
-        <v>125</v>
+        <v>773</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,12 +3338,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1330782670</t>
+          <t>1956967552</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330782670</t>
+          <t>https://m.place.naver.com/place/1956967552</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3368,29 +3360,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>시월의 네일</t>
+          <t>멜리플루</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>chltys1@naver.com</t>
+          <t>sycep@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1368-1165</t>
+          <t>0507-1388-1137</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로105길 22 시월의 네일</t>
+          <t>대구광역시 북구 대동로 38 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_DwWvb</t>
+          <t>https://toss.place/_lb/TYwXvAttF</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3400,7 +3392,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3425,13 +3417,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="Q32" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="R32" t="n">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,12 +3432,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1443846421</t>
+          <t>1330782670</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1443846421</t>
+          <t>https://m.place.naver.com/place/1330782670</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3462,34 +3454,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>푸키네일</t>
+          <t>시월의 네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>pooky_nail@naver.com</t>
+          <t>chltys1@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1379-9994</t>
+          <t>0507-1368-1165</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 415 메가타운 7층, 예쁘디예쁘다 안</t>
+          <t>대구광역시 북구 중앙대로105길 22 시월의 네일</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pooky_nail</t>
+          <t>http://pf.kakao.com/_DwWvb</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3510,7 +3502,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3519,13 +3511,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>483</v>
+        <v>11</v>
       </c>
       <c r="Q33" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="R33" t="n">
-        <v>535</v>
+        <v>25</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3534,12 +3526,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1189632296</t>
+          <t>1443846421</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189632296</t>
+          <t>https://m.place.naver.com/place/1443846421</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3556,29 +3548,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>위티네일</t>
+          <t>푸키네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jhjh9753@naver.com</t>
+          <t>pooky_nail@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1438-6646</t>
+          <t>0507-1379-9994</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로9길 5 1층 위티네일</t>
+          <t>대구광역시 북구 학정로 415 메가타운 7층, 예쁘디예쁘다 안</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/witty.nail/</t>
+          <t>https://www.instagram.com/pooky_nail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3604,7 +3596,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3613,13 +3605,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>20</v>
+        <v>483</v>
       </c>
       <c r="Q34" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="R34" t="n">
-        <v>50</v>
+        <v>535</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3628,12 +3620,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1037598797</t>
+          <t>1189632296</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037598797</t>
+          <t>https://m.place.naver.com/place/1189632296</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3650,29 +3642,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nail Vivienne</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>spotv_sports@naver.com</t>
-        </is>
-      </c>
+          <t>위티네일</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1352-1254</t>
+          <t>0507-1438-6646</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 북구 한강로 72-1 비비엔느네일</t>
+          <t>대구광역시 북구 성북로9길 5 1층 위티네일</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/witty.nail/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3682,7 +3670,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3698,22 +3686,22 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="R35" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3722,12 +3710,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1234676332</t>
+          <t>1037598797</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1234676332</t>
+          <t>https://m.place.naver.com/place/1037598797</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -3838,29 +3826,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>뷰티스공간</t>
+          <t>프롬퀸 네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jwifem@naver.com</t>
+          <t>promqueen0912@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1347-8607</t>
+          <t>0507-1396-5688</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 100 오페라삼정 그린코아더베스트 상가동 107호</t>
+          <t>대구광역시 북구 칠곡중앙대로77길 31-3</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_gongan</t>
+          <t>https://blog.naver.com/promqueen0912</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3875,7 +3863,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3886,7 +3874,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3895,13 +3883,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>113</v>
+        <v>260</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3910,12 +3898,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1680122870</t>
+          <t>1449308514</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1680122870</t>
+          <t>https://m.place.naver.com/place/1449308514</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -3932,29 +3920,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>몽뎅네일스튜디오</t>
+          <t>뷰티스공간</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>pk2hee@naver.com</t>
+          <t>jwifem@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1314-6829</t>
+          <t>0507-1347-8607</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정동로 40 한라하우젠트2차 상가</t>
+          <t>대구광역시 북구 침산로 100 오페라삼정 그린코아더베스트 상가동 107호</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mongdeng_nail</t>
+          <t>https://www.instagram.com/beauty_gongan</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3989,13 +3977,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="R38" t="n">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4004,12 +3992,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1973307356</t>
+          <t>1680122870</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973307356</t>
+          <t>https://m.place.naver.com/place/1680122870</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4026,29 +4014,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>데이즈네일</t>
+          <t>몽뎅네일스튜디오</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pungkang82@naver.com</t>
+          <t>pk2hee@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1355-6444</t>
+          <t>0507-1314-6829</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로65길 52 3층</t>
+          <t>대구광역시 북구 학정동로 40 한라하우젠트2차 상가</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/daze.nail_/</t>
+          <t>https://www.instagram.com/mongdeng_nail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4083,13 +4071,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>170</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="R39" t="n">
-        <v>31</v>
+        <v>181</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4098,12 +4086,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1089749071</t>
+          <t>1973307356</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1089749071</t>
+          <t>https://m.place.naver.com/place/1973307356</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4459,13 +4447,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="Q43" t="n">
         <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4647,13 +4635,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q45" t="n">
         <v>94</v>
       </c>
       <c r="R45" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4684,29 +4672,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>하까네일&amp;래쉬</t>
+          <t>그래비네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>bluefrog385@naver.com</t>
+          <t>foryou48613@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>0507-1394-0637</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학남로 9 1층 하까네일&amp;래쉬</t>
+          <t>대구광역시 북구 대천로18길 21 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hakkanail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4716,7 +4700,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4737,17 +4721,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="Q46" t="n">
         <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4756,12 +4740,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1721951293</t>
+          <t>1564740881</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1721951293</t>
+          <t>https://m.place.naver.com/place/1564740881</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -4872,25 +4856,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>그래비네일</t>
+          <t>하까네일&amp;래쉬</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>foryou48613@naver.com</t>
+          <t>bluefrog385@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1394-0637</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로18길 21 1층</t>
+          <t>대구광역시 북구 학남로 9 1층 하까네일&amp;래쉬</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/hakkanail</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4900,7 +4888,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4921,17 +4909,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="Q48" t="n">
         <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4940,12 +4928,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1564740881</t>
+          <t>1721951293</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564740881</t>
+          <t>https://m.place.naver.com/place/1721951293</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5056,34 +5044,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>올링네일</t>
+          <t>루미포레네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>youngeun120@naver.com</t>
+          <t>uilll77@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1313-2265</t>
+          <t>0507-1377-3829</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로24길 40 칠곡2차 영남타운 입구 옆 도로상가 올링네일</t>
+          <t>대구광역시 북구 동북로 163 202동 107호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/orling.nail?igsh=NnZkcjJjdzBhdXJz&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_xhpAyn</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5104,7 +5092,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5113,13 +5101,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5128,12 +5116,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1236901851</t>
+          <t>2023409739</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236901851</t>
+          <t>https://m.place.naver.com/place/2023409739</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5150,34 +5138,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>루미포레네일</t>
+          <t>올링네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>uilll77@naver.com</t>
+          <t>youngeun120@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1377-3829</t>
+          <t>0507-1313-2265</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 163 202동 107호</t>
+          <t>대구광역시 북구 팔거천동로24길 40 칠곡2차 영남타운 입구 옆 도로상가 올링네일</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhpAyn</t>
+          <t>https://www.instagram.com/orling.nail?igsh=NnZkcjJjdzBhdXJz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5198,7 +5186,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5207,13 +5195,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="R51" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5222,12 +5210,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2023409739</t>
+          <t>1236901851</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023409739</t>
+          <t>https://m.place.naver.com/place/1236901851</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5620,29 +5608,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>비니뷰티샵</t>
+          <t>에즈인뷰티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>cllctmmt@naver.com</t>
+          <t>aboutdearme@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1423-7769</t>
+          <t>0507-1321-7029</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로109길 12 1층</t>
+          <t>대구광역시 북구 침산로 246 1층 에즈인뷰티</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s3QEI0nh</t>
+          <t>https://www.instagram.com/az.in_b/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5677,13 +5665,13 @@
         </is>
       </c>
       <c r="P56" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q56" t="n">
         <v>14</v>
       </c>
-      <c r="Q56" t="n">
-        <v>36</v>
-      </c>
       <c r="R56" t="n">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5692,12 +5680,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1794625110</t>
+          <t>1797804703</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1794625110</t>
+          <t>https://m.place.naver.com/place/1797804703</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -5714,29 +5702,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>에즈인뷰티</t>
+          <t>채희뷰티 침산점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>aboutdearme@naver.com</t>
+          <t>chaehyejung1@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1321-7029</t>
+          <t>0507-1359-0318</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 246 1층 에즈인뷰티</t>
+          <t>대구광역시 북구 고성로 142 3층 301호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/az.in_b/</t>
+          <t>https://www.instagram.com/chaehee_beauty_sol</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5771,13 +5759,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="Q57" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5786,12 +5774,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1797804703</t>
+          <t>2020966033</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797804703</t>
+          <t>https://m.place.naver.com/place/2020966033</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -5808,29 +5796,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>채희뷰티 침산점</t>
+          <t>소이네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>chaehyejung1@naver.com</t>
+          <t>bin1549@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1359-0318</t>
+          <t>0507-1352-3577</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 북구 고성로 142 3층 301호</t>
+          <t>대구광역시 북구 옥산로 95 1층 114호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaehee_beauty_sol</t>
+          <t>https://www.instagram.com/soee.nail?igsh=c3NqcjZzMWZsZWk1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5856,7 +5844,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5865,13 +5853,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5880,12 +5868,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2020966033</t>
+          <t>2045962730</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020966033</t>
+          <t>https://m.place.naver.com/place/2045962730</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -5902,29 +5890,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>소이네일</t>
+          <t>알미네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>bin1549@naver.com</t>
+          <t>reina_99@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1352-3577</t>
+          <t>0507-1487-3656</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 북구 옥산로 95 1층 114호</t>
+          <t>대구광역시 북구 칠곡중앙대로53길 24 1층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soee.nail?igsh=c3NqcjZzMWZsZWk1&amp;utm_source=qr</t>
+          <t>http://instagram.com/ar_my_nail</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5944,13 +5932,17 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5959,13 +5951,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5974,12 +5966,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2045962730</t>
+          <t>1406194751</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045962730</t>
+          <t>https://m.place.naver.com/place/1406194751</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -5996,25 +5988,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>알미네일</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>네일 르 마지</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>hihy925@naver.com</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1487-3656</t>
+          <t>0507-1360-8063</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로53길 24 1층</t>
+          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀오피스텔 상가 2층 201호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>http://instagram.com/ar_my_nail</t>
+          <t>https://www.instagram.com/nail_lemazi</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6034,14 +6030,10 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>O</t>
@@ -6053,13 +6045,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R60" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6068,12 +6060,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1406194751</t>
+          <t>1295693572</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406194751</t>
+          <t>https://m.place.naver.com/place/1295693572</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6090,29 +6082,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일 르 마지</t>
+          <t>네일바다</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>hihy925@naver.com</t>
+          <t>kiwi10041010@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1360-8063</t>
+          <t>0507-1317-2364</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀오피스텔 상가 2층 201호</t>
+          <t>대구광역시 북구 칠곡중앙대로108길 21 1층 네일바다</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lemazi</t>
+          <t>http://instagram.com/nail.bada</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6138,7 +6130,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6147,13 +6139,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>193</v>
+        <v>2</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6162,12 +6154,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1295693572</t>
+          <t>1756678430</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1295693572</t>
+          <t>https://m.place.naver.com/place/1756678430</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6184,29 +6176,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일바다</t>
+          <t>이든네일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kiwi10041010@naver.com</t>
+          <t>ansdkfma0822@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1317-2364</t>
+          <t>0507-1381-2723</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로108길 21 1층 네일바다</t>
+          <t>대구광역시 북구 고성북로 34 오페라트루엘시민의숲 상가 201호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.bada</t>
+          <t>https://www.instagram.com/edeun_nail</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6241,13 +6233,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>2</v>
+        <v>162</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6256,12 +6248,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1756678430</t>
+          <t>1221641229</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756678430</t>
+          <t>https://m.place.naver.com/place/1221641229</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6278,29 +6270,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>이든네일</t>
+          <t>네일은너야</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ansdkfma0822@naver.com</t>
+          <t>555__555@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1381-2723</t>
+          <t>0507-1446-7912</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 북구 고성북로 34 오페라트루엘시민의숲 상가 201호</t>
+          <t>대구광역시 북구 팔거천동로26길 4-11 1층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/edeun_nail</t>
+          <t>http://instagram.com/nailyou053</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6335,13 +6327,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="Q63" t="n">
         <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>162</v>
+        <v>12</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6350,12 +6342,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1221641229</t>
+          <t>1112212009</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221641229</t>
+          <t>https://m.place.naver.com/place/1112212009</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6377,7 +6369,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0722kk_@naver.com</t>
+          <t>hhoney0824@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>

--- a/naver-place-crawler/results_nail/북구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/북구_네일샵.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한나네일</t>
+          <t>네일블링츠</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>raffinemoon@naver.com</t>
+          <t>yena0512@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1337-5971</t>
+          <t>0507-1339-0862</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대현남로2길 51 한나네일 1층</t>
+          <t>대구광역시 북구 태암로5길 13-1 1층 102호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hanna._.nail_</t>
+          <t>https://www.instagram.com/blinks_nail</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="R2" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1202246897</t>
+          <t>1424529823</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1202246897</t>
+          <t>https://m.place.naver.com/place/1424529823</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>어제오늘네일</t>
+          <t>온유뷰티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ksunmi88@naver.com</t>
+          <t>nbc9896@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1384-2440</t>
+          <t>0507-1433-0601</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동암로 110 3층 어제오늘네일</t>
+          <t>대구광역시 북구 칠성남로 30 상가동 102호 온유뷰티</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yeto.nail2</t>
+          <t>https://instagram.com/on._u_beauty?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>712</v>
+        <v>69</v>
       </c>
       <c r="Q3" t="n">
-        <v>184</v>
+        <v>10</v>
       </c>
       <c r="R3" t="n">
-        <v>896</v>
+        <v>79</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1950980170</t>
+          <t>1391715445</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1950980170</t>
+          <t>https://m.place.naver.com/place/1391715445</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,30 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미닛트 네일</t>
+          <t>Orly 네일&amp;피부 NC엑스코점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dmsghk057@naver.com</t>
+          <t>orlynail@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>053-383-4144</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로126길 7-12 105호</t>
+          <t>대구광역시 북구 유통단지로14길 22 NC코엑스점 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/minute_nail_/</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -785,7 +789,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="Q4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="R4" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1139512492</t>
+          <t>36704522</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139512492</t>
+          <t>https://m.place.naver.com/place/36704522</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일블링츠</t>
+          <t>바이느와르네일 칠성점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yena0512@naver.com</t>
+          <t>hhoney0824@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1339-0862</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태암로5길 13-1 1층 102호</t>
+          <t>대구광역시 북구 중앙대로 513 대구오페라클래시아 2층 206호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/blinks_nail</t>
+          <t>https://www.instagram.com/bynoir__nail_hj</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="R5" t="n">
-        <v>52</v>
+        <v>242</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1424529823</t>
+          <t>1236270675</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1424529823</t>
+          <t>https://m.place.naver.com/place/1236270675</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -936,29 +936,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>플로우네일케어</t>
+          <t>네일리즈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>frhlkfhkly3@naver.com</t>
+          <t>nail8500@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1356-1202</t>
+          <t>0507-1392-4881</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>대구광역시 북구 연경지묘로 6 1층 108호</t>
+          <t>대구광역시 북구 구암로39길 18-3 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flow_nail_care/</t>
+          <t>https://www.instagram.com/nail_rizz_</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1644153139</t>
+          <t>1403873554</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1644153139</t>
+          <t>https://m.place.naver.com/place/1403873554</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1030,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>뷰랩</t>
+          <t>오아이뷰티</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>miheynog@naver.com</t>
+          <t>mycutegod@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1417-9885</t>
+          <t>0507-1339-2823</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동천로 97 영남네오빌아트 106동 앞 상가</t>
+          <t>대구광역시 북구 칠성남로 70 근린생활시설 207호(2층)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/viewlab</t>
+          <t>http://www.instagram.com/oi_b.room</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1390</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>681</v>
+        <v>21</v>
       </c>
       <c r="R7" t="n">
-        <v>2071</v>
+        <v>31</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1602365195</t>
+          <t>1302335033</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1602365195</t>
+          <t>https://m.place.naver.com/place/1302335033</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>네일서아르</t>
+          <t>은뷰티</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>k_0608@naver.com</t>
+          <t>bazilamy@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1414-5027</t>
+          <t>0507-1366-9360</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 246 1층 네일서아르</t>
+          <t>대구광역시 북구 침산로22길 5 102동 112호 은뷰티</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_seoar</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1172,22 +1172,22 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>249</v>
+        <v>50</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="R8" t="n">
-        <v>255</v>
+        <v>81</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1748877111</t>
+          <t>2094752142</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1748877111</t>
+          <t>https://m.place.naver.com/place/2094752142</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>은뷰티</t>
+          <t>뷰랩</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bazilamy@naver.com</t>
+          <t>miheynog@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1366-9360</t>
+          <t>0507-1417-9885</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로22길 5 102동 112호 은뷰티</t>
+          <t>대구광역시 북구 동천로 97 영남네오빌아트 106동 앞 상가</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/viewlab</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49</v>
+        <v>1390</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>679</v>
       </c>
       <c r="R9" t="n">
-        <v>80</v>
+        <v>2069</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2094752142</t>
+          <t>1602365195</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2094752142</t>
+          <t>https://m.place.naver.com/place/1602365195</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1312,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일도 왁싱</t>
+          <t>올링네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vanhada_beauty@naver.com</t>
+          <t>youngeun120@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1395-1355</t>
+          <t>0507-1313-2265</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로 70 상가동 2층 210호</t>
+          <t>대구광역시 북구 팔거천동로24길 40 칠곡2차 영남타운 입구 옆 도로상가 올링네일</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://카카오톡오픈채팅을시작해보세요.링크를선택하면카카오톡이실행됩니다.네일도왁싱https//open.kakao.com/o/suNdDW4g</t>
+          <t>https://www.instagram.com/orling.nail?igsh=NnZkcjJjdzBhdXJz&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1360,7 +1360,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>262</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="R10" t="n">
-        <v>381</v>
+        <v>42</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1384,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1132125501</t>
+          <t>1236901851</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1132125501</t>
+          <t>https://m.place.naver.com/place/1236901851</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1406,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>민이네일</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>lee_dormery@naver.com</t>
-        </is>
-      </c>
+          <t>네일유</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1405-3361</t>
+          <t>0507-1343-1995</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대동로 50 1층</t>
+          <t>대구광역시 북구 구암로42길 10 101호 NAIL,U</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_mi.ni_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,7 +1434,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1459,17 +1455,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1474,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1867922573</t>
+          <t>1772663419</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867922573</t>
+          <t>https://m.place.naver.com/place/1772663419</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1500,25 +1496,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일플루이</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>nailpluie@naver.com</t>
-        </is>
-      </c>
+          <t>애몽</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1332-4233</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로110길 19 1층</t>
+          <t>대구광역시 북구 매전로 50-14 1층, 애몽</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailpluie</t>
+          <t>https://www.instagram.com/nail_aemong</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1533,7 +1529,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1553,13 +1549,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>8</v>
+        <v>560</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="R12" t="n">
-        <v>18</v>
+        <v>594</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1974701574</t>
+          <t>1174913259</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1974701574</t>
+          <t>https://m.place.naver.com/place/1174913259</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1586,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>코코수네일 복현점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>alsxm777@naver.com</t>
-        </is>
-      </c>
+          <t>네일바다</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1458-1158</t>
+          <t>0507-1317-2364</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대학로23길 10 2층</t>
+          <t>대구광역시 북구 칠곡중앙대로108길 21 1층 네일바다</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cocosu_nail/</t>
+          <t>http://instagram.com/nail.bada</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1647,13 +1639,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>173</v>
+        <v>2</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1654,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1621329974</t>
+          <t>1756678430</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1621329974</t>
+          <t>https://m.place.naver.com/place/1756678430</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1676,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>네일디보티</t>
+          <t>그래비네일</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1022eunji@naver.com</t>
+          <t>foryou48613@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>053-351-7622</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀 상가106호</t>
+          <t>대구광역시 북구 대천로18길 21 1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_devotee</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1716,7 +1704,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1737,17 +1725,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="Q14" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1744,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>37604636</t>
+          <t>1564740881</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37604636</t>
+          <t>https://m.place.naver.com/place/1564740881</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1778,34 +1766,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>살롱드302</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>hanseon216@naver.com</t>
-        </is>
-      </c>
+          <t>에즈인뷰티</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1366-7799</t>
+          <t>0507-1321-7029</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 434 2층 206호 살롱드302</t>
+          <t>대구광역시 북구 침산로 246 1층 에즈인뷰티</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://linkfly.to/70627DEJDap</t>
+          <t>https://www.instagram.com/az.in_b/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1826,22 +1810,22 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>395</v>
+        <v>98</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R15" t="n">
-        <v>406</v>
+        <v>112</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1834,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1472140745</t>
+          <t>1797804703</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1472140745</t>
+          <t>https://m.place.naver.com/place/1797804703</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1872,25 +1856,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아띠네일</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>attinail_@naver.com</t>
-        </is>
-      </c>
+          <t>뮤니크네일</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1375-6408</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호국로57길 31-12 1층 아띠네일</t>
+          <t>대구광역시 북구 팔거천동로34길 16-19 1층 뮤니크네일</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/munick_nail</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1900,7 +1884,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1921,17 +1905,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R16" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,17 +1924,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1088451483</t>
+          <t>1805790304</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088451483</t>
+          <t>https://m.place.naver.com/place/1805790304</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1962,29 +1946,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일105 복현 본점</t>
+          <t>뷰티셀럽연경점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nail105@naver.com</t>
+          <t>jyj-0@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1324-0222</t>
+          <t>053-985-2727</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 223 1층</t>
+          <t>대구광역시 북구 연경지묘로 6 셈텀타워 107호</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail.105</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1994,7 +1978,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2015,17 +1999,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1342</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1382</v>
+        <v>17</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2018,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1205043851</t>
+          <t>1606012647</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1205043851</t>
+          <t>https://m.place.naver.com/place/1606012647</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2056,29 +2040,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에이네일</t>
+          <t>네일리</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>hajw0129@naver.com</t>
+          <t>ysbfly@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1489-5668</t>
+          <t>0507-1388-7339</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 426 하나은행건물 3층</t>
+          <t>대구광역시 북구 태전로7길 10-17 두성타운상가 1층 네일리</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.nail0</t>
+          <t>https://www.instagram.com/nailee_nr</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2113,13 +2097,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>161</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2112,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1014010899</t>
+          <t>1928391317</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1014010899</t>
+          <t>https://m.place.naver.com/place/1928391317</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2150,34 +2134,34 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>온유뷰티</t>
+          <t>마이영네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nhbnhb05@naver.com</t>
+          <t>yujinlee10@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1433-0601</t>
+          <t>053-952-7172</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 30 상가동 102호 온유뷰티</t>
+          <t>대구광역시 북구 동북로53길 14-2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://instagram.com/on._u_beauty?igshid=YmMyMTA2M2Y=</t>
+          <t>http://pf.kakao.com/_xnYzxbxb</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2198,7 +2182,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2207,13 +2191,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R19" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2206,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1391715445</t>
+          <t>1489887782</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391715445</t>
+          <t>https://m.place.naver.com/place/1489887782</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2228,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에이무드뷰티</t>
+          <t>엔케어센터 복현점 /내성발톱/발각질/무좀발톱/젤네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sunsun900@naver.com</t>
+          <t>ncarecenter@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1398-7711</t>
+          <t>0507-1326-8241</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로106길 2 2층</t>
+          <t>대구광역시 북구 동북로 244 12층 1206호</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/amoodnail</t>
+          <t>http://abalico.co.kr</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2301,13 +2285,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>38</v>
+        <v>707</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="R20" t="n">
-        <v>54</v>
+        <v>774</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2300,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1257508634</t>
+          <t>1956967552</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1257508634</t>
+          <t>https://m.place.naver.com/place/1956967552</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2338,34 +2322,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>가비뷰티</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>dadalover0407@naver.com</t>
-        </is>
-      </c>
+          <t>미닛트 네일</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1315-8548</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태전로3길 17-1 1층 (태전동)</t>
+          <t>대구광역시 북구 칠곡중앙대로126길 7-12 105호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_evbSxj</t>
+          <t>https://www.instagram.com/minute_nail_/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2386,7 +2362,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2395,13 +2371,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2386,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1054977148</t>
+          <t>1139512492</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1054977148</t>
+          <t>https://m.place.naver.com/place/1139512492</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2432,29 +2408,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일리</t>
+          <t>플로우네일케어</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ysbfly@naver.com</t>
+          <t>frhlkfhkly3@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1388-7339</t>
+          <t>0507-1356-1202</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태전로7길 10-17 두성타운상가 1층 네일리</t>
+          <t>대구광역시 북구 연경지묘로 6 1층 108호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailee_nr</t>
+          <t>https://www.instagram.com/flow_nail_care/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2489,13 +2465,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2480,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1928391317</t>
+          <t>1644153139</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928391317</t>
+          <t>https://m.place.naver.com/place/1644153139</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2526,39 +2502,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>네일라쥬르</t>
+          <t>멜리플루</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dkenl0103@naver.com</t>
+          <t>sycep@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1371-0767</t>
+          <t>0507-1388-1137</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로 223</t>
+          <t>대구광역시 북구 대동로 38 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lasure_nail</t>
+          <t>https://toss.place/_lb/TYwXvAttF</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2574,7 +2550,7 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2583,13 +2559,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="Q23" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="R23" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2574,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1303390693</t>
+          <t>1330782670</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303390693</t>
+          <t>https://m.place.naver.com/place/1330782670</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2620,34 +2596,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아우라모이네일</t>
+          <t>가비뷰티</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nailhiro@naver.com</t>
+          <t>dadalover0407@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1365-8361</t>
+          <t>0507-1315-8548</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로 70 상가동 212호</t>
+          <t>대구광역시 북구 태전로3길 17-1 1층 (태전동)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailhiro</t>
+          <t>http://pf.kakao.com/_evbSxj</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2657,7 +2633,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2677,13 +2653,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2668,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2020256127</t>
+          <t>1054977148</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020256127</t>
+          <t>https://m.place.naver.com/place/1054977148</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2714,30 +2690,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>마이영네일</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>네일디보티</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1022eunji@naver.com</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>053-952-7172</t>
+          <t>053-351-7622</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로53길 14-2</t>
+          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀 상가106호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xnYzxbxb</t>
+          <t>http://www.instagram.com/nail_devotee</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2758,7 +2738,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2767,13 +2747,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="R25" t="n">
-        <v>131</v>
+        <v>26</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2762,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1489887782</t>
+          <t>37604636</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1489887782</t>
+          <t>https://m.place.naver.com/place/37604636</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2804,25 +2784,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>구르미네일</t>
+          <t>아띠네일</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1344-0696</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로116길 24 1층 구르미네일</t>
+          <t>대구광역시 북구 호국로57길 31-12 1층 아띠네일</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://instagram.com/9reumi_nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2832,7 +2808,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2853,17 +2829,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2872,17 +2848,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1928346749</t>
+          <t>1088451483</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928346749</t>
+          <t>https://m.place.naver.com/place/1088451483</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2894,35 +2870,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>유어메리뷰티</t>
+          <t>그리다네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1378-9783</t>
+          <t>0507-1369-9356</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>대구광역시 북구 복현로20길 2 1층</t>
+          <t>대구광역시 북구 대동로1길 75 1층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_mBAAn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2938,22 +2914,22 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="R27" t="n">
-        <v>159</v>
+        <v>63</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2962,17 +2938,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1050332478</t>
+          <t>1281503156</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050332478</t>
+          <t>https://m.place.naver.com/place/1281503156</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2984,29 +2960,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>화야네일앤뷰티</t>
+          <t>알미네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sbsb100488@naver.com</t>
+          <t>reina_99@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1319-6498</t>
+          <t>0507-1487-3656</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔달로35길 4 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로53길 24 1층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/hwaya_beauty</t>
+          <t>http://instagram.com/ar_my_nail</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3026,10 +3002,14 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/profile</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>O</t>
@@ -3041,13 +3021,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="Q28" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="R28" t="n">
-        <v>311</v>
+        <v>183</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3056,17 +3036,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1283528001</t>
+          <t>1406194751</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283528001</t>
+          <t>https://m.place.naver.com/place/1406194751</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3078,34 +3058,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>뮤니크네일</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>meohaseyo@naver.com</t>
-        </is>
-      </c>
+          <t>모제스튜디오</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1375-6408</t>
+          <t>0507-1360-2673</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로34길 16-19 1층 뮤니크네일</t>
+          <t>대구광역시 북구 침산남로31길 1 1층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/munick_nail</t>
+          <t>https://www.instagram.com/moje_nailstudio?igsh=emdzbm4xMmJhd2dl</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3115,7 +3091,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3126,7 +3102,7 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3135,13 +3111,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>8</v>
+        <v>921</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,17 +3126,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1805790304</t>
+          <t>1258515201</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805790304</t>
+          <t>https://m.place.naver.com/place/1258515201</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3172,34 +3148,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>더채온</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ameliepink@naver.com</t>
-        </is>
-      </c>
+          <t>네일도 왁싱</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1337-9853</t>
+          <t>0507-1395-1355</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로32길 11-7 2층</t>
+          <t>대구광역시 북구 성북로 70 상가동 2층 210호</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_rxfquX</t>
+          <t>https://카카오톡오픈채팅을시작해보세요.링크를선택하면카카오톡이실행됩니다.네일도왁싱https//open.kakao.com/o/suNdDW4g</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3229,13 +3201,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>9</v>
+        <v>262</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="R30" t="n">
-        <v>10</v>
+        <v>381</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3244,17 +3216,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2038014369</t>
+          <t>1132125501</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2038014369</t>
+          <t>https://m.place.naver.com/place/1132125501</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3266,29 +3238,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>엔케어센터 복현점 /내성발톱/발각질/무좀발톱/젤네일</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>ncarecenter@naver.com</t>
-        </is>
-      </c>
+          <t>어제오늘네일</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1326-8241</t>
+          <t>0507-1384-2440</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 244 12층 1206호</t>
+          <t>대구광역시 북구 동암로 110 3층 어제오늘네일</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://abalico.co.kr</t>
+          <t>https://www.instagram.com/yeto.nail2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3323,13 +3291,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="Q31" t="n">
-        <v>67</v>
+        <v>177</v>
       </c>
       <c r="R31" t="n">
-        <v>773</v>
+        <v>888</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,17 +3306,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1956967552</t>
+          <t>1950980170</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1956967552</t>
+          <t>https://m.place.naver.com/place/1950980170</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3360,39 +3328,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>멜리플루</t>
+          <t>투모로우바이뷰티</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sycep@naver.com</t>
+          <t>yunsm04@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0507-1388-1137</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대동로 38 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로67길 20 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TYwXvAttF</t>
+          <t>https://www.instagram.com/tomorrow.by.beauty</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3408,7 +3372,7 @@
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3417,13 +3381,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>102</v>
+        <v>587</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>215</v>
       </c>
       <c r="R32" t="n">
-        <v>125</v>
+        <v>802</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3396,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1330782670</t>
+          <t>1006662497</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1330782670</t>
+          <t>https://m.place.naver.com/place/1006662497</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3454,34 +3418,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>시월의 네일</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>chltys1@naver.com</t>
-        </is>
-      </c>
+          <t>에이무드뷰티</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1368-1165</t>
+          <t>0507-1398-7711</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로105길 22 시월의 네일</t>
+          <t>대구광역시 북구 중앙대로106길 2 2층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_DwWvb</t>
+          <t>https://www.instagram.com/amoodnail</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3502,7 +3462,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3511,13 +3471,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R33" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,17 +3486,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1443846421</t>
+          <t>1257508634</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1443846421</t>
+          <t>https://m.place.naver.com/place/1257508634</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3548,34 +3508,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>푸키네일</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>pooky_nail@naver.com</t>
-        </is>
-      </c>
+          <t>세니요미</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1379-9994</t>
+          <t>0507-1471-0523</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정로 415 메가타운 7층, 예쁘디예쁘다 안</t>
+          <t>대구광역시 북구 대천로7길 6-16 1층 세니요미</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pooky_nail</t>
+          <t>https://instabio.cc/4021506dbM8cU</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3596,7 +3552,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3605,13 +3561,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>483</v>
+        <v>265</v>
       </c>
       <c r="Q34" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="R34" t="n">
-        <v>535</v>
+        <v>350</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3620,17 +3576,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1189632296</t>
+          <t>1033303518</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1189632296</t>
+          <t>https://m.place.naver.com/place/1033303518</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3642,25 +3598,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>위티네일</t>
+          <t>뷰티스공간</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1438-6646</t>
+          <t>0507-1347-8607</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로9길 5 1층 위티네일</t>
+          <t>대구광역시 북구 침산로 100 오페라삼정 그린코아더베스트 상가동 107호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/witty.nail/</t>
+          <t>https://www.instagram.com/beauty_gongan</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3686,7 +3642,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3695,13 +3651,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Q35" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="R35" t="n">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3710,17 +3666,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1037598797</t>
+          <t>1680122870</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1037598797</t>
+          <t>https://m.place.naver.com/place/1680122870</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3732,39 +3688,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>네일유</t>
+          <t>시월의 네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nail_u123@naver.com</t>
+          <t>chltys1@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1343-1995</t>
+          <t>0507-1368-1165</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로42길 10 101호 NAIL,U</t>
+          <t>대구광역시 북구 중앙대로105길 22 시월의 네일</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_DwWvb</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3780,22 +3736,22 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="R36" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,17 +3760,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1772663419</t>
+          <t>1443846421</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772663419</t>
+          <t>https://m.place.naver.com/place/1443846421</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3826,29 +3782,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>프롬퀸 네일</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>promqueen0912@naver.com</t>
-        </is>
-      </c>
+          <t>소이네일</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1396-5688</t>
+          <t>0507-1352-3577</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로77길 31-3</t>
+          <t>대구광역시 북구 옥산로 95 1층 114호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/promqueen0912</t>
+          <t>https://www.instagram.com/soee.nail?igsh=c3NqcjZzMWZsZWk1&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3863,7 +3815,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3874,7 +3826,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3883,13 +3835,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>263</v>
+        <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3898,17 +3850,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1449308514</t>
+          <t>2045962730</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1449308514</t>
+          <t>https://m.place.naver.com/place/2045962730</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3920,34 +3872,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>뷰티스공간</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>jwifem@naver.com</t>
-        </is>
-      </c>
+          <t>네일바이비</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1347-8607</t>
+          <t>0507-1307-1576</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 100 오페라삼정 그린코아더베스트 상가동 107호</t>
+          <t>대구광역시 북구 대학로23길 16-4 1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_gongan</t>
+          <t>http://pf.kakao.com/_vBYPK</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3968,7 +3916,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3977,13 +3925,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="Q38" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="R38" t="n">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3992,17 +3940,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1680122870</t>
+          <t>1814661870</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1680122870</t>
+          <t>https://m.place.naver.com/place/1814661870</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4014,29 +3962,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>몽뎅네일스튜디오</t>
+          <t>네일라쥬르</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>pk2hee@naver.com</t>
+          <t>dkenl0103@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1314-6829</t>
+          <t>0507-1371-0767</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정동로 40 한라하우젠트2차 상가</t>
+          <t>대구광역시 북구 팔달로 223</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mongdeng_nail</t>
+          <t>https://www.instagram.com/lasure_nail</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4071,13 +4019,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>170</v>
+        <v>38</v>
       </c>
       <c r="Q39" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="R39" t="n">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4086,17 +4034,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1973307356</t>
+          <t>1303390693</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1973307356</t>
+          <t>https://m.place.naver.com/place/1303390693</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4108,34 +4056,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>네일드민</t>
+          <t>아우라모이네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>alswl990324@naver.com</t>
+          <t>nailhiro@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1487-8770</t>
+          <t>0507-1365-8361</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 북구 관음중앙로22길 5 1층</t>
+          <t>대구광역시 북구 성북로 70 상가동 212호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pwxnnn</t>
+          <t>https://blog.naver.com/nailhiro</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4145,7 +4093,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4165,13 +4113,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R40" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4180,17 +4128,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1595309498</t>
+          <t>2020256127</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1595309498</t>
+          <t>https://m.place.naver.com/place/2020256127</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4202,29 +4150,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일피오나</t>
+          <t>위티네일</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>cjrut2674@naver.com</t>
+          <t>jhjh9753@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1364-8481</t>
+          <t>0507-1438-6646</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매전로4길 22 1층 네일 피오나</t>
+          <t>대구광역시 북구 성북로9길 5 1층 위티네일</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_piona</t>
+          <t>https://www.instagram.com/witty.nail/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4250,7 +4198,7 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4259,13 +4207,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="R41" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4274,17 +4222,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1410565139</t>
+          <t>1037598797</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1410565139</t>
+          <t>https://m.place.naver.com/place/1037598797</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4296,29 +4244,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>모리앤네일</t>
+          <t>아메리네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>whatever21@naver.com</t>
+          <t>hankyuldata@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1362-4607</t>
+          <t>0507-1395-1991</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로 70 침산화성파크드림1008동 상가2층 222호</t>
+          <t>대구광역시 북구 동화천로57길 13 카노빌 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ameri_nail</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4328,7 +4276,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4349,17 +4297,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>8</v>
+        <v>285</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>9</v>
+        <v>289</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4368,17 +4316,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1109464508</t>
+          <t>1998879951</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1109464508</t>
+          <t>https://m.place.naver.com/place/1998879951</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4390,29 +4338,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>모제스튜디오</t>
+          <t>갓네일 &amp; 뷰티 대구역점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>possam-@naver.com</t>
+          <t>god_nail_2000@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1360-2673</t>
+          <t>0507-1432-2418</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로31길 1 1층</t>
+          <t>대구광역시 북구 중앙대로 513 2층 202호 갓네일 대구역점</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moje_nailstudio?igsh=emdzbm4xMmJhd2dl</t>
+          <t>https://www.instagram.com/god_nail_8000</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4438,7 +4386,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4447,13 +4395,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>914</v>
+        <v>457</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>98</v>
       </c>
       <c r="R43" t="n">
-        <v>919</v>
+        <v>555</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4462,17 +4410,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1258515201</t>
+          <t>1364996819</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258515201</t>
+          <t>https://m.place.naver.com/place/1364996819</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4484,29 +4432,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>오아이뷰티</t>
+          <t>민이네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mycutegod@naver.com</t>
+          <t>lee_dormery@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1339-2823</t>
+          <t>0507-1405-3361</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠성남로 70 근린생활시설 207호(2층)</t>
+          <t>대구광역시 북구 대동로 50 1층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/oi_b.room</t>
+          <t>https://www.instagram.com/_mi.ni_nail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4541,13 +4489,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4556,17 +4504,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1302335033</t>
+          <t>1867922573</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1302335033</t>
+          <t>https://m.place.naver.com/place/1867922573</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4578,34 +4526,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>갓네일 &amp; 뷰티 대구역점</t>
+          <t>네일드민</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>god_nail_2000@naver.com</t>
+          <t>alswl990324@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1432-2418</t>
+          <t>0507-1487-8770</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로 513 2층 202호 갓네일 대구역점</t>
+          <t>대구광역시 북구 관음중앙로22길 5 1층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/god_nail_8000</t>
+          <t>http://pf.kakao.com/_pwxnnn</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4626,7 +4574,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4635,13 +4583,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>450</v>
+        <v>9</v>
       </c>
       <c r="Q45" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>544</v>
+        <v>9</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,17 +4598,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1364996819</t>
+          <t>1595309498</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1364996819</t>
+          <t>https://m.place.naver.com/place/1595309498</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4672,25 +4620,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>그래비네일</t>
+          <t>레몬 네일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>foryou48613@naver.com</t>
+          <t>gorgeous_na_@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1430-2811</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로18길 21 1층</t>
+          <t>대구광역시 북구 호국로43길 27 . 상가 1층 북측</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lemon___nail</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4700,7 +4652,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4721,17 +4673,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="Q46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4740,17 +4692,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1564740881</t>
+          <t>1070857201</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1564740881</t>
+          <t>https://m.place.naver.com/place/1070857201</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4762,29 +4714,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>네일다니</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>nail_dani@naver.com</t>
-        </is>
-      </c>
+          <t>채희뷰티 침산점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1326-6288</t>
+          <t>0507-1359-0318</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>대구광역시 북구 태암남로11길 28-1 네일다니</t>
+          <t>대구광역시 북구 고성로 142 3층 301호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail_dani</t>
+          <t>https://www.instagram.com/chaehee_beauty_sol</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4799,7 +4747,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4819,13 +4767,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>414</v>
+        <v>9</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>438</v>
+        <v>11</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,17 +4782,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1058398706</t>
+          <t>2020966033</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1058398706</t>
+          <t>https://m.place.naver.com/place/2020966033</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4856,29 +4804,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>하까네일&amp;래쉬</t>
+          <t>에이네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>bluefrog385@naver.com</t>
+          <t>hajw0129@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1394-0637</t>
+          <t>0507-1489-5668</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학남로 9 1층 하까네일&amp;래쉬</t>
+          <t>대구광역시 북구 학정로 426 하나은행건물 3층</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hakkanail</t>
+          <t>https://www.instagram.com/a.nail0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4913,13 +4861,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="R48" t="n">
-        <v>138</v>
+        <v>40</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4928,17 +4876,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1721951293</t>
+          <t>1014010899</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1721951293</t>
+          <t>https://m.place.naver.com/place/1014010899</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4950,34 +4898,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>아메리네일</t>
+          <t>네일수미</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hankyuldata@naver.com</t>
+          <t>rawith0411@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1395-1991</t>
+          <t>0507-1362-2568</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동화천로57길 13 카노빌 1층</t>
+          <t>대구광역시 북구 성북로 8 1F 18호</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ameri_nail</t>
+          <t>http://pf.kakao.com/_SIxixlxj</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4998,7 +4946,7 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5007,13 +4955,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>285</v>
+        <v>141</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>289</v>
+        <v>146</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5022,17 +4970,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1998879951</t>
+          <t>1461190392</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1998879951</t>
+          <t>https://m.place.naver.com/place/1461190392</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5044,34 +4992,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>루미포레네일</t>
+          <t>이든네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>uilll77@naver.com</t>
+          <t>ansdkfma0822@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1377-3829</t>
+          <t>0507-1381-2723</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 163 202동 107호</t>
+          <t>대구광역시 북구 고성북로 34 오페라트루엘시민의숲 상가 201호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhpAyn</t>
+          <t>https://www.instagram.com/edeun_nail</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5092,7 +5040,7 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5101,13 +5049,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="Q50" t="n">
         <v>2</v>
       </c>
       <c r="R50" t="n">
-        <v>68</v>
+        <v>162</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5116,17 +5064,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>2023409739</t>
+          <t>1221641229</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023409739</t>
+          <t>https://m.place.naver.com/place/1221641229</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5138,29 +5086,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>올링네일</t>
+          <t>구르미네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>youngeun120@naver.com</t>
+          <t>gurmi_nail_240624@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1313-2265</t>
+          <t>0507-1344-0696</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로24길 40 칠곡2차 영남타운 입구 옆 도로상가 올링네일</t>
+          <t>대구광역시 북구 칠곡중앙대로116길 24 1층 구르미네일</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/orling.nail?igsh=NnZkcjJjdzBhdXJz&amp;utm_source=qr</t>
+          <t>http://instagram.com/9reumi_nail</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5195,13 +5143,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5210,17 +5158,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1236901851</t>
+          <t>1928346749</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236901851</t>
+          <t>https://m.place.naver.com/place/1928346749</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5232,29 +5180,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일리즈</t>
+          <t>네일다니</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>taehana0426@naver.com</t>
+          <t>nail_dani@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1392-4881</t>
+          <t>0507-1326-6288</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로39길 18-3 1층</t>
+          <t>대구광역시 북구 태암남로11길 28-1 네일다니</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_rizz_</t>
+          <t>https://blog.naver.com/nail_dani</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5269,7 +5217,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5280,7 +5228,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5289,13 +5237,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>72</v>
+        <v>414</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="R52" t="n">
-        <v>75</v>
+        <v>438</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5304,17 +5252,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1403873554</t>
+          <t>1058398706</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1403873554</t>
+          <t>https://m.place.naver.com/place/1058398706</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5326,29 +5274,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>레몬 네일</t>
+          <t>공원옆네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>gorgeous_na_@naver.com</t>
+          <t>hymizzang@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1430-2811</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>대구광역시 북구 호국로43길 27 . 상가 1층 북측</t>
+          <t>대구광역시 북구 구암로21길 37 302동 208호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lemon___nail</t>
+          <t>https://www.instagram.com/nail.park_</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5383,13 +5327,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5398,17 +5342,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1070857201</t>
+          <t>1948302097</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070857201</t>
+          <t>https://m.place.naver.com/place/1948302097</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5420,29 +5364,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>그리다네일</t>
+          <t>몽뎅네일스튜디오</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>gridanail2@naver.com</t>
+          <t>pk2hee@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1369-9356</t>
+          <t>0507-1314-6829</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대동로1길 75 1층</t>
+          <t>대구광역시 북구 학정동로 40 한라하우젠트2차 상가</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/mongdeng_nail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5452,7 +5396,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5473,17 +5417,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>35</v>
+        <v>170</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="R54" t="n">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5492,17 +5436,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1281503156</t>
+          <t>1973307356</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1281503156</t>
+          <t>https://m.place.naver.com/place/1973307356</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5514,34 +5458,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>레푸스 칠곡점</t>
+          <t>모카네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hjw8125@naver.com</t>
+          <t>daonnail0305@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1319-8125</t>
+          <t>0507-1446-1569</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 244 3층</t>
+          <t>대구광역시 북구 학정동로13길 3 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hjw8125</t>
+          <t>http://pf.kakao.com/_xcubwn</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -5551,7 +5495,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5562,22 +5506,22 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>151</v>
+        <v>501</v>
       </c>
       <c r="Q55" t="n">
-        <v>356</v>
+        <v>12</v>
       </c>
       <c r="R55" t="n">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5586,17 +5530,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1036282232</t>
+          <t>1744601857</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036282232</t>
+          <t>https://m.place.naver.com/place/1744601857</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5608,29 +5552,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>에즈인뷰티</t>
+          <t>네일서아르</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>aboutdearme@naver.com</t>
+          <t>k_0608@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1321-7029</t>
+          <t>0507-1414-5027</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 246 1층 에즈인뷰티</t>
+          <t>대구광역시 북구 침산로 246 1층 네일서아르</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/az.in_b/</t>
+          <t>https://www.instagram.com/nail_seoar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5665,13 +5609,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>98</v>
+        <v>249</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="R56" t="n">
-        <v>112</v>
+        <v>255</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5680,17 +5624,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1797804703</t>
+          <t>1748877111</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797804703</t>
+          <t>https://m.place.naver.com/place/1748877111</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5702,29 +5646,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>채희뷰티 침산점</t>
+          <t>네일 르 마지</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>chaehyejung1@naver.com</t>
+          <t>hihy925@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1359-0318</t>
+          <t>0507-1360-8063</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>대구광역시 북구 고성로 142 3층 301호</t>
+          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀오피스텔 상가 2층 201호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaehee_beauty_sol</t>
+          <t>https://www.instagram.com/nail_lemazi</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5759,13 +5703,13 @@
         </is>
       </c>
       <c r="P57" t="n">
+        <v>186</v>
+      </c>
+      <c r="Q57" t="n">
         <v>8</v>
       </c>
-      <c r="Q57" t="n">
-        <v>2</v>
-      </c>
       <c r="R57" t="n">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5774,17 +5718,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>2020966033</t>
+          <t>1295693572</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020966033</t>
+          <t>https://m.place.naver.com/place/1295693572</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5796,29 +5740,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>소이네일</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>bin1549@naver.com</t>
-        </is>
-      </c>
+          <t>설레는 네일</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1352-3577</t>
+          <t>0507-1460-0172</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>대구광역시 북구 옥산로 95 1층 114호</t>
+          <t>대구광역시 북구 동북로 131 양우내안에아파트 상가 1층</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/soee.nail?igsh=c3NqcjZzMWZsZWk1&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/sullem_mn</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5853,13 +5793,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="R58" t="n">
-        <v>1</v>
+        <v>274</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5868,17 +5808,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>2045962730</t>
+          <t>1264344506</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2045962730</t>
+          <t>https://m.place.naver.com/place/1264344506</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5890,34 +5830,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>알미네일</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>reina_99@naver.com</t>
-        </is>
-      </c>
+          <t>더채온</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1487-3656</t>
+          <t>0507-1337-9853</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로53길 24 1층</t>
+          <t>대구광역시 북구 침산로32길 11-7 2층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>http://instagram.com/ar_my_nail</t>
+          <t>http://pf.kakao.com/_rxfquX</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5932,14 +5868,10 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/profile</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>O</t>
@@ -5951,13 +5883,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>168</v>
+        <v>10</v>
       </c>
       <c r="Q59" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>181</v>
+        <v>11</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5966,17 +5898,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1406194751</t>
+          <t>2038014369</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1406194751</t>
+          <t>https://m.place.naver.com/place/2038014369</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5988,29 +5920,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>네일 르 마지</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>hihy925@naver.com</t>
-        </is>
-      </c>
+          <t>한나네일</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1360-8063</t>
+          <t>0507-1337-5971</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로21길 39 태왕아너스로뎀오피스텔 상가 2층 201호</t>
+          <t>대구광역시 북구 대현남로2길 51 한나네일 1층</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lemazi</t>
+          <t>https://www.instagram.com/hanna._.nail_</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6036,7 +5964,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6045,13 +5973,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>185</v>
+        <v>65</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="R60" t="n">
-        <v>193</v>
+        <v>100</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6060,17 +5988,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1295693572</t>
+          <t>1202246897</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1295693572</t>
+          <t>https://m.place.naver.com/place/1202246897</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6082,29 +6010,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>네일바다</t>
+          <t>컨티뉴페이스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kiwi10041010@naver.com</t>
+          <t>oncepromd@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1317-2364</t>
+          <t>0507-1358-0463</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로108길 21 1층 네일바다</t>
+          <t>대구광역시 북구 칠곡중앙대로 434 대구읍내행복주택 상가 2층 205호 &lt;지하주차무료&gt;</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail.bada</t>
+          <t>https://www.instagram.com/continewface_nail?igsh=YWhvMzgweWY2Zmhp</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6139,13 +6067,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1</v>
+        <v>769</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>881</v>
       </c>
       <c r="R61" t="n">
-        <v>2</v>
+        <v>1650</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6154,17 +6082,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1756678430</t>
+          <t>1991303123</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1756678430</t>
+          <t>https://m.place.naver.com/place/1991303123</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6176,29 +6104,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>이든네일</t>
+          <t>화야네일앤뷰티</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ansdkfma0822@naver.com</t>
+          <t>sbsb100488@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1381-2723</t>
+          <t>0507-1319-6498</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>대구광역시 북구 고성북로 34 오페라트루엘시민의숲 상가 201호</t>
+          <t>대구광역시 북구 팔달로35길 4 1층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/edeun_nail</t>
+          <t>http://www.instagram.com/hwaya_beauty</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6224,7 +6152,7 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6233,13 +6161,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="R62" t="n">
-        <v>162</v>
+        <v>311</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6248,17 +6176,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1221641229</t>
+          <t>1283528001</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1221641229</t>
+          <t>https://m.place.naver.com/place/1283528001</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6270,34 +6198,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일은너야</t>
+          <t>코코수네일 복현점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>555__555@naver.com</t>
+          <t>alsxm777@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1446-7912</t>
+          <t>0507-1458-1158</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>대구광역시 북구 팔거천동로26길 4-11 1층</t>
+          <t>대구광역시 북구 대학로23길 10 2층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailyou053</t>
+          <t>https://www.instagram.com/cocosu_nail/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6307,7 +6235,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6327,13 +6255,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R63" t="n">
-        <v>12</v>
+        <v>173</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6342,17 +6270,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1112212009</t>
+          <t>1621329974</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1112212009</t>
+          <t>https://m.place.naver.com/place/1621329974</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6364,25 +6292,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>바이느와르네일 칠성점</t>
+          <t>채희뷰티</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>hhoney0824@naver.com</t>
+          <t>chaehee_beauty@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1414-6681</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>대구광역시 북구 중앙대로 513 대구오페라클래시아 2층 206호</t>
+          <t>대구광역시 북구 동북로 247 상가동 2층 210호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bynoir__nail_hj</t>
+          <t>https://www.instagram.com/chaehee_beauty</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6408,7 +6340,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6417,13 +6349,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>131</v>
+        <v>526</v>
       </c>
       <c r="Q64" t="n">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="R64" t="n">
-        <v>238</v>
+        <v>577</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6432,17 +6364,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1236270675</t>
+          <t>1030745191</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236270675</t>
+          <t>https://m.place.naver.com/place/1030745191</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6454,30 +6386,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일,해주연</t>
+          <t>네일105 복현 본점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>vely_sohee@naver.com</t>
+          <t>nail105@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1324-0222</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매전로4길 31 매천동753</t>
+          <t>대구광역시 북구 동북로 223 1층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_nzuin</t>
+          <t>http://www.instagram.com/nail.105</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6498,22 +6434,22 @@
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>87</v>
+        <v>1343</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="R65" t="n">
-        <v>88</v>
+        <v>1383</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6522,17 +6458,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2041500566</t>
+          <t>1205043851</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2041500566</t>
+          <t>https://m.place.naver.com/place/1205043851</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6544,29 +6480,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>리리네일</t>
+          <t>프롬퀸 네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>hime_s2@naver.com</t>
+          <t>promqueen0912@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1379-6902</t>
+          <t>0507-1396-5688</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정동로 76 1층</t>
+          <t>대구광역시 북구 칠곡중앙대로77길 31-3</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hime_s2</t>
+          <t>https://blog.naver.com/promqueen0912</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6592,7 +6528,7 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6601,13 +6537,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>131</v>
+        <v>260</v>
       </c>
       <c r="Q66" t="n">
-        <v>160</v>
+        <v>3</v>
       </c>
       <c r="R66" t="n">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6616,17 +6552,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1536988597</t>
+          <t>1449308514</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1536988597</t>
+          <t>https://m.place.naver.com/place/1449308514</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6638,34 +6574,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일바이비</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>jin_a_diary@naver.com</t>
-        </is>
-      </c>
+          <t>하까네일&amp;래쉬</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1307-1576</t>
+          <t>0507-1394-0637</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대학로23길 16-4 1층</t>
+          <t>대구광역시 북구 학남로 9 1층 하까네일&amp;래쉬</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_vBYPK</t>
+          <t>https://www.instagram.com/hakkanail</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -6686,7 +6618,7 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6695,13 +6627,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>27</v>
+        <v>134</v>
       </c>
       <c r="Q67" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="R67" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6710,17 +6642,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1814661870</t>
+          <t>1721951293</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814661870</t>
+          <t>https://m.place.naver.com/place/1721951293</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6732,29 +6664,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>컨티뉴페이스</t>
+          <t>푸키네일</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>oncepromd@naver.com</t>
+          <t>pooky_nail@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1358-0463</t>
+          <t>0507-1379-9994</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로 434 대구읍내행복주택 상가 2층 205호 &lt;지하주차무료&gt;</t>
+          <t>대구광역시 북구 학정로 415 메가타운 7층, 예쁘디예쁘다 안</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/continewface_nail?igsh=YWhvMzgweWY2Zmhp</t>
+          <t>https://www.instagram.com/pooky_nail</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6789,13 +6721,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>769</v>
+        <v>483</v>
       </c>
       <c r="Q68" t="n">
-        <v>881</v>
+        <v>52</v>
       </c>
       <c r="R68" t="n">
-        <v>1650</v>
+        <v>535</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6804,17 +6736,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1991303123</t>
+          <t>1189632296</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1991303123</t>
+          <t>https://m.place.naver.com/place/1189632296</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6826,34 +6758,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>애몽</t>
+          <t>유어메리뷰티</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>emong0902@naver.com</t>
+          <t>multtang1@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1332-4233</t>
+          <t>0507-1378-9783</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>대구광역시 북구 매전로 50-14 1층, 애몽</t>
+          <t>대구광역시 북구 복현로20길 2 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_aemong</t>
+          <t>http://pf.kakao.com/_mBAAn</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6874,7 +6806,7 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6883,13 +6815,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>554</v>
+        <v>157</v>
       </c>
       <c r="Q69" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>588</v>
+        <v>159</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6898,17 +6830,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1174913259</t>
+          <t>1050332478</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174913259</t>
+          <t>https://m.place.naver.com/place/1050332478</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6920,29 +6852,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>세니요미</t>
+          <t>네일,해주연</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sennny@naver.com</t>
+          <t>vely_sohee@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>0507-1471-0523</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>대구광역시 북구 대천로7길 6-16 1층 세니요미</t>
+          <t>대구광역시 북구 매전로4길 31 매천동753</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://instabio.cc/4021506dbM8cU</t>
+          <t>http://pf.kakao.com/_nzuin</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6973,17 +6901,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>265</v>
+        <v>87</v>
       </c>
       <c r="Q70" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>350</v>
+        <v>88</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6992,17 +6920,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1033303518</t>
+          <t>2041500566</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033303518</t>
+          <t>https://m.place.naver.com/place/2041500566</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7014,12 +6942,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>공원옆네일</t>
+          <t>네일플루이</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>hymizzang@naver.com</t>
+          <t>nailpluie@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -7027,12 +6955,12 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>대구광역시 북구 구암로21길 37 302동 208호</t>
+          <t>대구광역시 북구 칠곡중앙대로110길 19 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail.park_</t>
+          <t>https://blog.naver.com/nailpluie</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7047,7 +6975,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7067,13 +6995,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R71" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7082,17 +7010,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1948302097</t>
+          <t>1974701574</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1948302097</t>
+          <t>https://m.place.naver.com/place/1974701574</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7104,29 +7032,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>채희뷰티</t>
+          <t>레푸스 칠곡점</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>chaehee_beauty@naver.com</t>
+          <t>hjw8125@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1414-6681</t>
+          <t>0507-1319-8125</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 247 상가동 2층 210호</t>
+          <t>대구광역시 북구 칠곡중앙대로 244 3층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chaehee_beauty</t>
+          <t>https://blog.naver.com/hjw8125</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7141,7 +7069,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7152,22 +7080,22 @@
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>527</v>
+        <v>151</v>
       </c>
       <c r="Q72" t="n">
-        <v>51</v>
+        <v>356</v>
       </c>
       <c r="R72" t="n">
-        <v>578</v>
+        <v>507</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7176,17 +7104,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1030745191</t>
+          <t>1036282232</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1030745191</t>
+          <t>https://m.place.naver.com/place/1036282232</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7198,30 +7126,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>투모로우바이뷰티</t>
+          <t>루미포레네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>yunsm04@naver.com</t>
+          <t>uilll77@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1377-3829</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>대구광역시 북구 칠곡중앙대로67길 20 1층</t>
+          <t>대구광역시 북구 동북로 163 202동 107호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tomorrow.by.beauty</t>
+          <t>http://pf.kakao.com/_xhpAyn</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7242,7 +7174,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7251,13 +7183,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>586</v>
+        <v>68</v>
       </c>
       <c r="Q73" t="n">
-        <v>215</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>801</v>
+        <v>70</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7266,17 +7198,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1006662497</t>
+          <t>2023409739</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1006662497</t>
+          <t>https://m.place.naver.com/place/2023409739</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7288,29 +7220,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일수미</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>rawith0411@naver.com</t>
-        </is>
-      </c>
+          <t>살롱드302</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1362-2568</t>
+          <t>0507-1366-7799</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>대구광역시 북구 성북로 8 1F 18호</t>
+          <t>대구광역시 북구 칠곡중앙대로 434 2층 206호 살롱드302</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_SIxixlxj</t>
+          <t>https://linkfly.to/70627DEJDap</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7336,22 +7264,22 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>141</v>
+        <v>395</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R74" t="n">
-        <v>146</v>
+        <v>406</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7360,17 +7288,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1461190392</t>
+          <t>1472140745</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1461190392</t>
+          <t>https://m.place.naver.com/place/1472140745</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7382,34 +7310,26 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>모카네일</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>daonnail0305@naver.com</t>
-        </is>
-      </c>
+          <t>낭만네일</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>0507-1446-1569</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>대구광역시 북구 학정동로13길 3 1층</t>
+          <t>대구광역시 북구 침산남로31길 11</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xcubwn</t>
+          <t>http://nangmannail.com</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -7430,7 +7350,7 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7439,13 +7359,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>499</v>
+        <v>25</v>
       </c>
       <c r="Q75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R75" t="n">
-        <v>511</v>
+        <v>36</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7454,17 +7374,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1744601857</t>
+          <t>1055429676</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1744601857</t>
+          <t>https://m.place.naver.com/place/1055429676</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7476,29 +7396,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>설레는 네일</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>daonnail0305@naver.com</t>
-        </is>
-      </c>
+          <t>모리앤네일</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1460-0172</t>
+          <t>0507-1362-4607</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 131 양우내안에아파트 상가 1층</t>
+          <t>대구광역시 북구 성북로 70 침산화성파크드림1008동 상가2층 222호</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sullem_mn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7508,7 +7424,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7529,17 +7445,17 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>253</v>
+        <v>8</v>
       </c>
       <c r="Q76" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>274</v>
+        <v>9</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7548,17 +7464,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1264344506</t>
+          <t>1109464508</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1264344506</t>
+          <t>https://m.place.naver.com/place/1109464508</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
